--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.2%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.0%</t>
+          <t>-571.7%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-238.0%</t>
+          <t>-238.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>-65.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-184.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.1%</t>
+          <t>-229.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-147.1%</t>
         </is>
       </c>
     </row>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88543246841229</v>
+        <v>-10.83594897715655</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.192775236227515</v>
+        <v>-1.172981839725221</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.575390372174662</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.83341695444348</v>
+        <v>-10.78393346318774</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.16797869495359</v>
+        <v>-1.148185298451295</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.579380707861062</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9750887961676</v>
+        <v>-10.92560530491186</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.226122658541979</v>
+        <v>-1.206329262039684</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.577905480962321</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92549795174276</v>
+        <v>-10.87601446048703</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.191232910607174</v>
+        <v>-1.171439514104879</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.594348827702643</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.622713397782093</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.72634584450566</v>
+        <v>-10.67686235324993</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.124623201359017</v>
+        <v>-1.104829804856722</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.42902630175283</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.708855779705298</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50050069178625</v>
+        <v>-10.45101720053052</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.024706067235044</v>
+        <v>-1.004912670732749</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.387099626165667</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.743590858093805</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.37592203544866</v>
+        <v>-10.32643854419292</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9737354601439487</v>
+        <v>-0.9539420636416529</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.387099626165667</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.744730002649864</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42881732349295</v>
+        <v>-10.37933383223721</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9922598011995554</v>
+        <v>-0.9724664046972604</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.38214428007722</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.750336984465039</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1449085925642</v>
+        <v>-10.09542510130846</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8729626045894197</v>
+        <v>-0.8531692080871238</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.38214428007722</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.756070688703676</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-10.02405870869881</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.8343599134371305</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.789153261875599</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-9.760221841494744</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.73870864786841</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.779269780562692</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.492980040626346</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.6336464880204247</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.777435220063318</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.395073001949855</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.594783987523289</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.242792137607016</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.817926355006191</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.371119460973897</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.5845340649874124</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.218838596631059</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.832966985737259</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.107059522651101</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.4921704058200458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.954778658308262</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.978142632569185</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.399979899146263</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.2121255900784118</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.954778658308262</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.975355598908884</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.359795600780073</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.1957082468440943</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-1.914594359942072</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.99980980181644</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.279725805242268</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.1643135074082154</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.834524564404268</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>2.047218500359879</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-8.046244583012669</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.0629965896785234</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.601043342174669</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.19523166253549</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-7.896578192005154</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>-0.00602224358847625</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.508139850932133</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.248081546968053</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-7.764302718374267</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>0.04225543261090525</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.375864377301247</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.322814317893612</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.573703043701115</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.1213103631678027</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.185264702628094</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.43998918338514</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.324703245017534</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.233816623864894</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.185264702628094</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.452895524608799</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.430293234790638</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>0.06360469835643379</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.290854692401198</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.261565601145718</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.449028136909235</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>0.104655079386081</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.290854692401198</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.310109943022804</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.301088095501636</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>0.04395217326095313</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.270533776492641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.202423569879771</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.276859459112663</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>0.04492964156306423</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.208246765459676</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.233311052341973</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>0.05538839217624725</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.201286153364583</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-6.991162658888115</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.1667101039389336</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.215748507745726</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-6.927933287119767</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.186533973105468</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.210280628204921</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-6.804642152302636</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.2333485210428972</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.123014005286538</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.281753403105776</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-6.783492953399192</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.2495091788415995</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.101864806383094</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.302143900685167</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.539727511415748</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.342796063982028</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.101864806383094</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.297924609032218</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.392830483697878</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.4036791889891918</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.328643868139387</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.142980089748804</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.4963614215525238</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.321385943123089</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-5.967087997281372</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.5703173820601455</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.324985066643738</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-5.795641534258908</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.6522234733236845</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-0.8827601013820433</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.441180450511769</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.570608534590085</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.741257150807511</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.6577271017132205</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.57522072792936</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.506972792356151</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.7714062487554019</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5940913594792859</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.618096974324038</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.413972751150252</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.7898005240215569</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5940913594792859</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.599291233107834</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.173542254345392</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.8877157993683782</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3536608626744256</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.745292607815627</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.101299686174197</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.9205421404716763</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3536608626744256</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.749221921650447</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-4.985359836549012</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.9675966642390905</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2768391316583018</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.795993544177462</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-4.876554951069285</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>1.008116689650975</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2768391316583018</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.792991615397455</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.656534153032275</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>1.097704045876393</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1356192865903215</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.879302559448857</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.523666463968997</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.166745304303527</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1356192865903215</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.895196742250681</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.364151360449627</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.231697190151577</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>0.02389581692904841</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.992051648802605</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.21947921534989</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.299654150752912</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.1685679620287858</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.088943038423887</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.279354042707582</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.261741711211261</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1086931346710937</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>3.039055633410698</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.192554544928573</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.318862003645431</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1086931346710937</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>3.061456126733264</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.195024251390379</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.31794652243412</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>0.1062234282092875</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>3.060046704229592</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.263394437714389</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.301605370379219</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.076619046126023</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.191461499343651</v>
+        <v>-4.141978008087912</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320815254359405</v>
+        <v>1.3406086508617</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>3.067055754757914</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.222454658672357</v>
+        <v>-4.172971167416618</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.13312755566831</v>
+        <v>1.152920952170605</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.891765319798301</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.046980398879887</v>
+        <v>-3.997496907624149</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207884491577085</v>
+        <v>1.227677888079381</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.896332551790089</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.157916651521136</v>
+        <v>-4.108433160265397</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.139252019281793</v>
+        <v>1.159045415784088</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.872074580551296</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.360943229064369</v>
+        <v>-4.31145973780863</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061172773484405</v>
+        <v>1.0809661699867</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.753390019245261</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.203017630129076</v>
+        <v>-4.153534138873337</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134515399490654</v>
+        <v>1.15430879599295</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.763562405677394</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.116774167102698</v>
+        <v>-4.06729067584696</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163959055275066</v>
+        <v>1.183752451777361</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.758508676251254</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.11795725175376</v>
+        <v>-4.068473760498021</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155261596859167</v>
+        <v>1.175054993361462</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09317049876424244</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.746898622615873</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.994829544759677</v>
+        <v>-3.945346053503938</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205064552689902</v>
+        <v>1.224857949192197</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09317049876424244</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.747450495648974</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.902019063308817</v>
+        <v>-3.852535572053079</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171461437161611</v>
+        <v>1.191254833663907</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.0003600173133830875</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.732409476410856</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.853456011087787</v>
+        <v>-3.803972519832048</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192760133974624</v>
+        <v>1.212553530476919</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>0.0482030349076471</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.763420783668075</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.740784792851537</v>
+        <v>-3.691301301595798</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.232904329780847</v>
+        <v>1.252697726283142</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1608742531438973</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.826099223121548</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628407791668864</v>
+        <v>-3.578924300413126</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.283346426084583</v>
+        <v>1.303139822586879</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1608742531438973</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.831590518952215</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.826642360555595</v>
+        <v>-3.777158869299856</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.21554980029843</v>
+        <v>1.235343196800726</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.03736031574283327</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.724146979388716</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.909643641580874</v>
+        <v>-3.860160150325135</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.020705007888972</v>
+        <v>1.040498404391268</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.551360168673065</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.750449369524298</v>
+        <v>-3.700965878268559</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.204532377430808</v>
+        <v>1.224325773933103</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.67150982939227</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.8370479525054</v>
+        <v>-3.787564461249662</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.18440597034069</v>
+        <v>1.204199366842985</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.686022855494593</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.798664289947249</v>
+        <v>-3.749180798691511</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.197178876706319</v>
+        <v>1.216972273208615</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01754753771185585</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.706472494371853</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.621547959912083</v>
+        <v>-3.572064468656345</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.264754437565687</v>
+        <v>1.284547834067983</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01754753771185585</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.703201523217154</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.59184583593579</v>
+        <v>-3.542362344680051</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.277318678918118</v>
+        <v>1.297112075420413</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.02201766292716922</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.70120283984988</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.412470414697022</v>
+        <v>-3.362986923441283</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.34285582272004</v>
+        <v>1.362649219222335</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.1347590952435495</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.789055870058725</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.457484628217628</v>
+        <v>-3.408001136961889</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.305657592643387</v>
+        <v>1.325450989145682</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>0.1044101999289448</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.751653988201552</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.724489138490063</v>
+        <v>-3.675005647234324</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.204547350873358</v>
+        <v>1.224340747375654</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.08995283811400373</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.640727727714729</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.013276358948978</v>
+        <v>-3.96379286769324</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.088236384586294</v>
+        <v>1.108029781088589</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1910389582130041</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.57927997755183</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.980800772778206</v>
+        <v>-3.931317281522468</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098826580608919</v>
+        <v>1.118619977111215</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1910389582130041</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.576879939106147</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.961762645070909</v>
+        <v>-3.91227915381517</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102966550900083</v>
+        <v>1.122759947402379</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2492225695441986</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.538494491515675</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.992889276221527</v>
+        <v>-3.943405784965788</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.268097767378517</v>
+        <v>1.287891163880812</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2492225695441986</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.716076360454355</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.045209656822318</v>
+        <v>-3.995726165566579</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.248002944124333</v>
+        <v>1.267796340626629</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2142757095353265</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.737877805445812</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.189532562747237</v>
+        <v>-4.140049071491498</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.196282312151292</v>
+        <v>1.216075708653587</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2142757095353265</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.743886335842738</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.041789592512234</v>
+        <v>-3.992306101256496</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.334532148037315</v>
+        <v>1.35432554453961</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.04646835230044333</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.92372339797569</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.143804275043456</v>
+        <v>-4.094320783787717</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.296519896556307</v>
+        <v>1.316313293058603</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.04646835230044333</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.926517019507171</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.007194930949364</v>
+        <v>-3.957711439693625</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.351825982585602</v>
+        <v>1.371619379087898</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>0.09014099179364915</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>3.009144974355285</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.149960263772014</v>
+        <v>-4.100476772516275</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.293800326196653</v>
+        <v>1.313593722698948</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.05262434102900126</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.922566251401805</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.750043945200545</v>
+        <v>3.840152547783123</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.09404757949664</v>
+        <v>-4.101042942148442</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.382500953703623</v>
+        <v>1.379702808642902</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.05262434102900126</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.988901805198626</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-687.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>440.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.7%</t>
+          <t>-592.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-275.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-66.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-238.3%</t>
+          <t>-246.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-65.8%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-184.7%</t>
+          <t>-213.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-229.3%</t>
+          <t>-236.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-147.1%</t>
+          <t>-151.3%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.8701886521770035</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.772896877142177</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-1.077754436568615</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.687695359504773</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.495508460115452</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.518520641591101</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.698797929437255</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.437071070461302</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.906801987790332</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.358761591673996</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-2.118214408678307</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.269278079656794</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.457372786266829</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.126699027927835</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.665863567718514</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.063641005085929</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.913064752483735</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>1.972859281588409</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.405449780507832</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.777011662422503</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.790630171437904</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.621482044863337</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-4.134312944664567</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.485778059027288</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.340824721551589</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.399279406928737</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.596665807330282</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.29871589931752</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-5.028471600480069</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.112326469525009</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.263165594612621</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.006733646874079</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.598828241843074</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.871049179637863</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.962454486743387</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.7320862419119791</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.327581869382134</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.5852898038623118</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.736170646562812</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.4206158370047994</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-7.012746746878644</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3051708293499273</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.429138621165642</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.1366081302440056</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.580842483270056</v>
+        <v>-7.805815631695486</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08618527607091897</v>
+        <v>-0.003803983299253133</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.926717305254865</v>
+        <v>-8.151690453680295</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05606508757730966</v>
+        <v>-0.1460543469474818</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.090297183439249</v>
+        <v>-8.31527033186468</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1230921187960621</v>
+        <v>-0.2130813781662346</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.386958525249447</v>
+        <v>-8.611931673674878</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2379776795909332</v>
+        <v>-0.3279669389611057</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.735176062890307</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.3812909991816804</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-9.118177451632938</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.5345936560003168</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.275576331846059</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.5949816921141351</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.635106654350061</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.7334435178176855</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.685455717804283</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.745667123242197</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.558101846800248</v>
+        <v>-9.783074995225679</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6916838242188144</v>
+        <v>-0.7816730835889865</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.554410921843838</v>
+        <v>-9.779384070269268</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.69020745423625</v>
+        <v>-0.7801967136064221</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.758669097173701</v>
+        <v>-9.983642245599132</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7663975272495529</v>
+        <v>-0.8563867866197254</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.976706868804879</v>
+        <v>-10.20168001723031</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8491300814175879</v>
+        <v>-0.93911934078776</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.90323703713743</v>
+        <v>-10.12821018556286</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8043704472571873</v>
+        <v>-0.8943597066273599</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07836145452397</v>
+        <v>-10.3033346029494</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8598649934642877</v>
+        <v>-0.9498542528344602</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31281354853846</v>
+        <v>-10.53778669696389</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9608649959716797</v>
+        <v>-1.050854255341852</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.6006173930757</v>
+        <v>-10.82559054150113</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.082658724560551</v>
+        <v>-1.172647983930724</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65340354867603</v>
+        <v>-10.87837669710146</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.102657396962126</v>
+        <v>-1.192646656332298</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.83594897715655</v>
+        <v>-11.11040561683772</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.172981839725221</v>
+        <v>-1.282764495597688</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.575390372174662</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.78393346318774</v>
+        <v>-11.05839010286891</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.148185298451295</v>
+        <v>-1.257967954323762</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.579380707861062</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.92560530491186</v>
+        <v>-11.20006194459303</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.206329262039684</v>
+        <v>-1.316111917912152</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.577905480962321</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.87601446048703</v>
+        <v>-11.15047110016819</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.171439514104879</v>
+        <v>-1.281222169977346</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.594348827702643</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.622713397782093</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.67686235324993</v>
+        <v>-10.95131899293109</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.104829804856722</v>
+        <v>-1.214612460729189</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.42902630175283</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.708855779705298</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.45101720053052</v>
+        <v>-10.72547384021168</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.004912670732749</v>
+        <v>-1.114695326605216</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.387099626165667</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.743590858093805</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.32643854419292</v>
+        <v>-10.60089518387409</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9539420636416529</v>
+        <v>-1.06372471951412</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.387099626165667</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.744730002649864</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.37933383223721</v>
+        <v>-10.65379047191838</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9724664046972604</v>
+        <v>-1.082249060569728</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.38214428007722</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.750336984465039</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.09542510130846</v>
+        <v>-10.36988174098963</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8531692080871238</v>
+        <v>-0.9629518639595913</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.38214428007722</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.756070688703676</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.02405870869881</v>
+        <v>-10.29851534837998</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8343599134371305</v>
+        <v>-0.9441425693095979</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.789153261875599</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.760221841494744</v>
+        <v>-10.03467848117591</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.73870864786841</v>
+        <v>-0.8484913037408774</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.779269780562692</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.492980040626346</v>
+        <v>-9.767436680307515</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6336464880204247</v>
+        <v>-0.7434291438928922</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.777435220063318</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.395073001949855</v>
+        <v>-9.669529641631025</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.594783987523289</v>
+        <v>-0.7045666433957569</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.242792137607016</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.817926355006191</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.371119460973897</v>
+        <v>-9.645576100655067</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5845340649874124</v>
+        <v>-0.6943167208598799</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.218838596631059</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.832966985737259</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.107059522651101</v>
+        <v>-9.38151616233227</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4921704058200458</v>
+        <v>-0.6019530616925133</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.954778658308262</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.978142632569185</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.399979899146263</v>
+        <v>-8.674436538827432</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2121255900784118</v>
+        <v>-0.3219082459508793</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.954778658308262</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.975355598908884</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.359795600780073</v>
+        <v>-8.634252240461242</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1957082468440943</v>
+        <v>-0.3054909027165618</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.914594359942072</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.99980980181644</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.279725805242268</v>
+        <v>-8.554182444923438</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1643135074082154</v>
+        <v>-0.2740961632806833</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.834524564404268</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.047218500359879</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.046244583012669</v>
+        <v>-8.320701222693838</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.0629965896785234</v>
+        <v>-0.1727792455509909</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.601043342174669</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.19523166253549</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.896578192005154</v>
+        <v>-8.171034831686324</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.00602224358847625</v>
+        <v>-0.1158048994609446</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.508139850932133</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.248081546968053</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.764302718374267</v>
+        <v>-8.038759358055437</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.04225543261090525</v>
+        <v>-0.06752722326156269</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.375864377301247</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.322814317893612</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.573703043701115</v>
+        <v>-7.848159683382284</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1213103631678027</v>
+        <v>0.01152770729533525</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.185264702628094</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.43998918338514</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.324703245017534</v>
+        <v>-7.599159884698703</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.233816623864894</v>
+        <v>0.1240339679924265</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.185264702628094</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.452895524608799</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.430293234790638</v>
+        <v>-7.704749874471807</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.06360469835643379</v>
+        <v>-0.04617795751603415</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.290854692401198</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.261565601145718</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.449028136909235</v>
+        <v>-7.723484776590404</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.104655079386081</v>
+        <v>-0.005127576486386509</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.290854692401198</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.310109943022804</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.301088095501636</v>
+        <v>-7.575544735182805</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.04395217326095313</v>
+        <v>-0.06583048261151436</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.270533776492641</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.202423569879771</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.276859459112663</v>
+        <v>-7.551316098793833</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.04492964156306423</v>
+        <v>-0.06485301430940371</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.208246765459676</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.233311052341973</v>
+        <v>-7.507767692023142</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05538839217624725</v>
+        <v>-0.05439426369622069</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.201286153364583</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.991162658888115</v>
+        <v>-7.265619298569284</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1667101039389336</v>
+        <v>0.05692744806646566</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.215748507745726</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.927933287119767</v>
+        <v>-7.202389926800936</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.186533973105468</v>
+        <v>0.0767513172330001</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.210280628204921</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.804642152302636</v>
+        <v>-7.079098791983805</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2333485210428972</v>
+        <v>0.1235658651704292</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.123014005286538</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.281753403105776</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.783492953399192</v>
+        <v>-7.057949593080362</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2495091788415995</v>
+        <v>0.139726522969132</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.101864806383094</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.302143900685167</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.539727511415748</v>
+        <v>-6.814184151096917</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.342796063982028</v>
+        <v>0.2330134081095605</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.101864806383094</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.297924609032218</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.392830483697878</v>
+        <v>-6.667287123379047</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4036791889891918</v>
+        <v>0.2938965331167243</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.328643868139387</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.142980089748804</v>
+        <v>-6.417436729429973</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4963614215525238</v>
+        <v>0.3865787656800563</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.321385943123089</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.967087997281372</v>
+        <v>-6.241544636962541</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5703173820601455</v>
+        <v>0.460534726187678</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.324985066643738</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.795641534258908</v>
+        <v>-6.070098173940077</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6522234733236845</v>
+        <v>0.542440817451217</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8827601013820433</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.441180450511769</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.570608534590085</v>
+        <v>-5.845065174271254</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.741257150807511</v>
+        <v>0.631474494935043</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6577271017132205</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.57522072792936</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.506972792356151</v>
+        <v>-5.78142943203732</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7714062487554019</v>
+        <v>0.6616235928829344</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5940913594792859</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.618096974324038</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.413972751150252</v>
+        <v>-5.688429390831422</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7898005240215569</v>
+        <v>0.6800178681490889</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5940913594792859</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.599291233107834</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.173542254345392</v>
+        <v>-5.447998894026561</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8877157993683782</v>
+        <v>0.7779331434959107</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3536608626744256</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.745292607815627</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.101299686174197</v>
+        <v>-5.375756325855367</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9205421404716763</v>
+        <v>0.8107594845992088</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3536608626744256</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.749221921650447</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.985359836549012</v>
+        <v>-5.259816476230181</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9675966642390905</v>
+        <v>0.8578140083666228</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2768391316583018</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.795993544177462</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.876554951069285</v>
+        <v>-5.151011590750454</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.008116689650975</v>
+        <v>0.8983340337785073</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2768391316583018</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.792991615397455</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.656534153032275</v>
+        <v>-4.930990792713444</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.097704045876393</v>
+        <v>0.9879213900039254</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1356192865903215</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.879302559448857</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.523666463968997</v>
+        <v>-4.798123103650166</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.166745304303527</v>
+        <v>1.05696264843106</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1356192865903215</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.895196742250681</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.364151360449627</v>
+        <v>-4.638608000130796</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.231697190151577</v>
+        <v>1.12191453427911</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.02389581692904841</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.992051648802605</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.21947921534989</v>
+        <v>-4.493935855031059</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.299654150752912</v>
+        <v>1.189871494880445</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1685679620287858</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.088943038423887</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.279354042707582</v>
+        <v>-4.553810682388751</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.261741711211261</v>
+        <v>1.151959055338793</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1086931346710937</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.039055633410698</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.192554544928573</v>
+        <v>-4.467011184609742</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.318862003645431</v>
+        <v>1.209079347772963</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1086931346710937</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.061456126733264</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.195024251390379</v>
+        <v>-4.469480891071548</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.31794652243412</v>
+        <v>1.208163866561653</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1062234282092875</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.060046704229592</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.263394437714389</v>
+        <v>-4.537851077395558</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.301605370379219</v>
+        <v>1.191822714506751</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.076619046126023</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.141978008087912</v>
+        <v>-4.416434647769082</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.3406086508617</v>
+        <v>1.230825994989233</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.067055754757914</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.172971167416618</v>
+        <v>-4.447427807097787</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.152920952170605</v>
+        <v>1.043138296298137</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.891765319798301</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.997496907624149</v>
+        <v>-4.271953547305317</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.227677888079381</v>
+        <v>1.117895232206913</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.896332551790089</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.108433160265397</v>
+        <v>-4.382889799946566</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.159045415784088</v>
+        <v>1.04926275991162</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.872074580551296</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.31145973780863</v>
+        <v>-4.5859163774898</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.0809661699867</v>
+        <v>0.9711835141142329</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.753390019245261</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.153534138873337</v>
+        <v>-4.427990778554507</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.15430879599295</v>
+        <v>1.044526140120482</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.763562405677394</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.06729067584696</v>
+        <v>-4.341747315528129</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.183752451777361</v>
+        <v>1.073969795904894</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.758508676251254</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.068473760498021</v>
+        <v>-4.34293040017919</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.175054993361462</v>
+        <v>1.065272337488995</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.09317049876424244</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.746898622615873</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.945346053503938</v>
+        <v>-4.219802693185107</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.224857949192197</v>
+        <v>1.115075293319729</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.09317049876424244</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.747450495648974</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.852535572053079</v>
+        <v>-4.126992211734247</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.191254833663907</v>
+        <v>1.081472177791439</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.0003600173133830875</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.732409476410856</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.803972519832048</v>
+        <v>-4.078429159513218</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.212553530476919</v>
+        <v>1.102770874604452</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.0482030349076471</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.763420783668075</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.691301301595798</v>
+        <v>-3.965757941276967</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.252697726283142</v>
+        <v>1.142915070410675</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1608742531438973</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.826099223121548</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.578924300413126</v>
+        <v>-3.853380940094295</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.303139822586879</v>
+        <v>1.193357166714411</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1608742531438973</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.831590518952215</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777158869299856</v>
+        <v>-4.051615508981025</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.235343196800726</v>
+        <v>1.125560540928258</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.03736031574283327</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.724146979388716</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.860160150325135</v>
+        <v>-4.134616790006304</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.040498404391268</v>
+        <v>0.9307157485187998</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.551360168673065</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.700965878268559</v>
+        <v>-3.975422517949728</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.224325773933103</v>
+        <v>1.114543118060636</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.67150982939227</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.787564461249662</v>
+        <v>-4.062021100930831</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.204199366842985</v>
+        <v>1.094416710970517</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.686022855494593</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.749180798691511</v>
+        <v>-4.02363743837268</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.216972273208615</v>
+        <v>1.107189617336147</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01754753771185585</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.706472494371853</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.572064468656345</v>
+        <v>-3.846521108337514</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.284547834067983</v>
+        <v>1.174765178195515</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01754753771185585</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.703201523217154</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.542362344680051</v>
+        <v>-3.816818984361221</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.297112075420413</v>
+        <v>1.187329419547946</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.02201766292716922</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.70120283984988</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.362986923441283</v>
+        <v>-3.637443563122453</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.362649219222335</v>
+        <v>1.252866563349867</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1347590952435495</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.789055870058725</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.408001136961889</v>
+        <v>-3.682457776643059</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.325450989145682</v>
+        <v>1.215668333273214</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1044101999289448</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.751653988201552</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.675005647234324</v>
+        <v>-3.949462286915495</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.224340747375654</v>
+        <v>1.114558091503186</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08995283811400373</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.640727727714729</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.96379286769324</v>
+        <v>-4.23824950737441</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.108029781088589</v>
+        <v>0.9982471252161211</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1910389582130041</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.57927997755183</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.931317281522468</v>
+        <v>-4.205773921203638</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.118619977111215</v>
+        <v>1.008837321238747</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1910389582130041</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.576879939106147</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.91227915381517</v>
+        <v>-4.18673579349634</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.122759947402379</v>
+        <v>1.012977291529911</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2492225695441986</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.538494491515675</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.943405784965788</v>
+        <v>-4.217862424646959</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.287891163880812</v>
+        <v>1.178108508008344</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2492225695441986</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.716076360454355</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.995726165566579</v>
+        <v>-4.27018280524775</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.267796340626629</v>
+        <v>1.158013684754161</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2142757095353265</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.737877805445812</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.140049071491498</v>
+        <v>-4.414505711172669</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.216075708653587</v>
+        <v>1.106293052781119</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2142757095353265</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.743886335842738</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.992306101256496</v>
+        <v>-4.266762740937667</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.35432554453961</v>
+        <v>1.244542888667142</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.04646835230044333</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.92372339797569</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.094320783787717</v>
+        <v>-4.368777423468888</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.316313293058603</v>
+        <v>1.206530637186134</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.04646835230044333</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.926517019507171</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864727</v>
+        <v>3.805605409864729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.957711439693625</v>
+        <v>-4.232168079374795</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.371619379087898</v>
+        <v>1.26183672321543</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.09014099179364915</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.009144974355285</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360611</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.100476772516275</v>
+        <v>-4.374933412197445</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.313593722698948</v>
+        <v>1.20381106682648</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.05262434102900126</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.922566251401805</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.840152547783123</v>
+        <v>3.574069546319763</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.101042942148442</v>
+        <v>-4.312635413421323</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.379702808642902</v>
+        <v>1.29506582013375</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.05262434102900126</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.988901805198626</v>
+        <v>2.94770342209875</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>128.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-687.9%</t>
+          <t>-687.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.9%</t>
+          <t>441.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-592.8%</t>
+          <t>-587.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.5%</t>
+          <t>-275.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.7%</t>
+          <t>-244.4%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>-65.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-184.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.1%</t>
+          <t>-229.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-158.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1970"/>
+  <dimension ref="A1:G1971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8701886521770035</v>
+        <v>-0.861090071840676</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.772896877142177</v>
+        <v>2.776536309276708</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.077754436568615</v>
+        <v>-1.068655856232288</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.687695359504773</v>
+        <v>2.691334791639304</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.495508460115452</v>
+        <v>-1.486409879779125</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.518520641591101</v>
+        <v>2.522160073725632</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.698797929437255</v>
+        <v>-1.689699349100928</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.437071070461302</v>
+        <v>2.440710502595833</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.906801987790332</v>
+        <v>-1.897703407454005</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.358761591673996</v>
+        <v>2.362401023808527</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.118214408678307</v>
+        <v>-2.10911582834198</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.269278079656794</v>
+        <v>2.272917511791325</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.457372786266829</v>
+        <v>-2.448274205930502</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.126699027927835</v>
+        <v>2.130338460062366</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.665863567718514</v>
+        <v>-2.656764987382187</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.063641005085929</v>
+        <v>2.06728043722046</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.913064752483735</v>
+        <v>-2.903966172147408</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.972859281588409</v>
+        <v>1.97649871372294</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.405449780507832</v>
+        <v>-3.396351200171505</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.777011662422503</v>
+        <v>1.780651094557034</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.790630171437904</v>
+        <v>-3.781531591101577</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.621482044863337</v>
+        <v>1.625121476997868</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.134312944664567</v>
+        <v>-4.12521436432824</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.485778059027288</v>
+        <v>1.489417491161819</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.340824721551589</v>
+        <v>-4.331726141215261</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.399279406928737</v>
+        <v>1.402918839063268</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.596665807330282</v>
+        <v>-4.587567226993954</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.29871589931752</v>
+        <v>1.30235533145205</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.028471600480069</v>
+        <v>-5.019373020143742</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.112326469525009</v>
+        <v>1.11596590165954</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.263165594612621</v>
+        <v>-5.254067014276294</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.006733646874079</v>
+        <v>1.01037307900861</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.598828241843074</v>
+        <v>-5.589729661506746</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.871049179637863</v>
+        <v>0.874688611772394</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.962454486743387</v>
+        <v>-5.95335590640706</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7320862419119791</v>
+        <v>0.7357256740465101</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.327581869382134</v>
+        <v>-6.318483289045806</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5852898038623118</v>
+        <v>0.5889292359968428</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.736170646562812</v>
+        <v>-6.727072066226485</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4206158370047994</v>
+        <v>0.42425526913933</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.012746746878644</v>
+        <v>-7.003648166542318</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3051708293499273</v>
+        <v>0.3088102614844579</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.429138621165642</v>
+        <v>-7.420040040829315</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1366081302440056</v>
+        <v>0.1402475623785362</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.805815631695486</v>
+        <v>-7.79671705135916</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.003803983299253133</v>
+        <v>-0.0001645511647225817</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.151690453680295</v>
+        <v>-8.142591873343969</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1460543469474818</v>
+        <v>-0.1424149148129512</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.31527033186468</v>
+        <v>-8.306171751528353</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2130813781662346</v>
+        <v>-0.2094419460317041</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.611931673674878</v>
+        <v>-8.602833093338552</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3279669389611057</v>
+        <v>-0.3243275068265752</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.735176062890307</v>
+        <v>-8.726077482553981</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3812909991816804</v>
+        <v>-0.3776515670471499</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.118177451632938</v>
+        <v>-9.109078871296612</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5345936560003168</v>
+        <v>-0.5309542238657863</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.275576331846059</v>
+        <v>-9.266477751509733</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5949816921141351</v>
+        <v>-0.5913422599796045</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.635106654350061</v>
+        <v>-9.626008074013734</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7334435178176855</v>
+        <v>-0.7298040856831549</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.685455717804283</v>
+        <v>-9.676357137467956</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.745667123242197</v>
+        <v>-0.7420276911076664</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.783074995225679</v>
+        <v>-9.773976414889352</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7816730835889865</v>
+        <v>-0.7780336514544559</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.779384070269268</v>
+        <v>-9.770285489932942</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7801967136064221</v>
+        <v>-0.7765572814718915</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.983642245599132</v>
+        <v>-9.974543665262805</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8563867866197254</v>
+        <v>-0.8527473544851949</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.20168001723031</v>
+        <v>-10.19258143689398</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.93911934078776</v>
+        <v>-0.9354799086532295</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.12821018556286</v>
+        <v>-10.11911160522653</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8943597066273599</v>
+        <v>-0.8907202744928293</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.3033346029494</v>
+        <v>-10.29423602261308</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9498542528344602</v>
+        <v>-0.9462148206999297</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.53778669696389</v>
+        <v>-10.52868811662757</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.050854255341852</v>
+        <v>-1.047214823207322</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.82559054150113</v>
+        <v>-10.81649196116481</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.172647983930724</v>
+        <v>-1.169008551796193</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.87837669710146</v>
+        <v>-10.86927811676513</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.192646656332298</v>
+        <v>-1.189007224197767</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.11040561683772</v>
+        <v>-11.05182354524566</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.282764495597688</v>
+        <v>-1.259331666960863</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.575390372174662</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05839010286891</v>
+        <v>-10.99980803127684</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.257967954323762</v>
+        <v>-1.234535125686937</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.579380707861062</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.20006194459303</v>
+        <v>-11.14147987300096</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.316111917912152</v>
+        <v>-1.292679089275326</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.643939672127477</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.577905480962321</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.15047110016819</v>
+        <v>-11.09188902857613</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.281222169977346</v>
+        <v>-1.257789341340521</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.594348827702643</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.622713397782093</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.95131899293109</v>
+        <v>-10.89273692133903</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.214612460729189</v>
+        <v>-1.191179632092364</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.42902630175283</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.708855779705298</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.72547384021168</v>
+        <v>-10.66689176861962</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.114695326605216</v>
+        <v>-1.091262497968391</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.387099626165667</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.743590858093805</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.60089518387409</v>
+        <v>-10.54231311228203</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.06372471951412</v>
+        <v>-1.040291890877296</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.387099626165667</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.744730002649864</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.65379047191838</v>
+        <v>-10.59520840032632</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.082249060569728</v>
+        <v>-1.058816231932902</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.38214428007722</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.750336984465039</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.36988174098963</v>
+        <v>-10.31129966939757</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9629518639595913</v>
+        <v>-0.9395190353227667</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.38214428007722</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.756070688703676</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.29851534837998</v>
+        <v>-10.23993327678792</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9441425693095979</v>
+        <v>-0.9207097406727724</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.789153261875599</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03467848117591</v>
+        <v>-9.97609640958385</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8484913037408774</v>
+        <v>-0.8250584751040524</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.779269780562692</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.767436680307515</v>
+        <v>-9.708854608715452</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7434291438928922</v>
+        <v>-0.7199963152560671</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.310777887467573</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.777435220063318</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.669529641631025</v>
+        <v>-9.610947570038961</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7045666433957569</v>
+        <v>-0.6811338147589314</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.242792137607016</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.817926355006191</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.645576100655067</v>
+        <v>-9.586994029063003</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6943167208598799</v>
+        <v>-0.6708838922230549</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.218838596631059</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.832966985737259</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.38151616233227</v>
+        <v>-9.322934090740207</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6019530616925133</v>
+        <v>-0.5785202330556882</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.954778658308262</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.978142632569185</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.674436538827432</v>
+        <v>-8.615854467235369</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3219082459508793</v>
+        <v>-0.2984754173140542</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.954778658308262</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.975355598908884</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.634252240461242</v>
+        <v>-8.575670168869179</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3054909027165618</v>
+        <v>-0.2820580740797367</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-1.914594359942072</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.99980980181644</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.554182444923438</v>
+        <v>-8.495600373331374</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2740961632806833</v>
+        <v>-0.2506633346438578</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.834524564404268</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>2.047218500359879</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.320701222693838</v>
+        <v>-8.262119151101775</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1727792455509909</v>
+        <v>-0.1493464169141658</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.601043342174669</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.19523166253549</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.171034831686324</v>
+        <v>-8.112452760094261</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1158048994609446</v>
+        <v>-0.09237207082411913</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.508139850932133</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.248081546968053</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.038759358055437</v>
+        <v>-7.980177286463374</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06752722326156269</v>
+        <v>-0.04409439462473763</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.375864377301247</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.322814317893612</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.848159683382284</v>
+        <v>-7.789577611790222</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01152770729533525</v>
+        <v>0.03496053593216031</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.185264702628094</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.43998918338514</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.599159884698703</v>
+        <v>-7.540577813106641</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1240339679924265</v>
+        <v>0.1474667966292516</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.185264702628094</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.452895524608799</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.704749874471807</v>
+        <v>-7.646167802879745</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04617795751603415</v>
+        <v>-0.0227451288792091</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.290854692401198</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.261565601145718</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.723484776590404</v>
+        <v>-7.664902704998342</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.005127576486386509</v>
+        <v>0.01830525215043854</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.290854692401198</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.310109943022804</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.575544735182805</v>
+        <v>-7.516962663590743</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.06583048261151436</v>
+        <v>-0.04239765397468931</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.270533776492641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.202423569879771</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.551316098793833</v>
+        <v>-7.49273402720177</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06485301430940371</v>
+        <v>-0.04142018567257866</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.208246765459676</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.507767692023142</v>
+        <v>-7.44918562043108</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05439426369622069</v>
+        <v>-0.03096143505939564</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.201286153364583</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.265619298569284</v>
+        <v>-7.207037226977222</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05692744806646566</v>
+        <v>0.08036027670329071</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.215748507745726</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.202389926800936</v>
+        <v>-7.143807855208873</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0767513172330001</v>
+        <v>0.1001841458698252</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.246305140103668</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.210280628204921</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.079098791983805</v>
+        <v>-7.020516720391742</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1235658651704292</v>
+        <v>0.1469986938072543</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.123014005286538</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.281753403105776</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.057949593080362</v>
+        <v>-6.999367521488299</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.139726522969132</v>
+        <v>0.1631593516059571</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.101864806383094</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.302143900685167</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.814184151096917</v>
+        <v>-6.755602079504855</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2330134081095605</v>
+        <v>0.2564462367463851</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.101864806383094</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.297924609032218</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.667287123379047</v>
+        <v>-6.608705051786984</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2938965331167243</v>
+        <v>0.3173293617535498</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.328643868139387</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.417436729429973</v>
+        <v>-6.358854657837909</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3865787656800563</v>
+        <v>0.4100115943168814</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.321385943123089</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.241544636962541</v>
+        <v>-6.182962565370477</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.460534726187678</v>
+        <v>0.483967554824503</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.054206564404506</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.324985066643738</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.070098173940077</v>
+        <v>-6.011516102348014</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.542440817451217</v>
+        <v>0.565873646088042</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-0.8827601013820433</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.441180450511769</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.845065174271254</v>
+        <v>-5.786483102679191</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.631474494935043</v>
+        <v>0.6549073235718685</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.6577271017132205</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.57522072792936</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.78142943203732</v>
+        <v>-5.722847360445257</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6616235928829344</v>
+        <v>0.6850564215197594</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5940913594792859</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.618096974324038</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.688429390831422</v>
+        <v>-5.629847319239358</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6800178681490889</v>
+        <v>0.7034506967859144</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5940913594792859</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.599291233107834</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.447998894026561</v>
+        <v>-5.389416822434498</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7779331434959107</v>
+        <v>0.8013659721327357</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3536608626744256</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.745292607815627</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.375756325855367</v>
+        <v>-5.317174254263303</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8107594845992088</v>
+        <v>0.8341923132360338</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3536608626744256</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.749221921650447</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.259816476230181</v>
+        <v>-5.201234404638118</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8578140083666228</v>
+        <v>0.8812468370034483</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2768391316583018</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.795993544177462</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.151011590750454</v>
+        <v>-5.092429519158391</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8983340337785073</v>
+        <v>0.9217668624153323</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2768391316583018</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.792991615397455</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.930990792713444</v>
+        <v>-4.87240872112138</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9879213900039254</v>
+        <v>1.011354218640751</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1356192865903215</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.879302559448857</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.798123103650166</v>
+        <v>-4.739541032058103</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.05696264843106</v>
+        <v>1.080395477067885</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1356192865903215</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.895196742250681</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.638608000130796</v>
+        <v>-4.580025928538733</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.12191453427911</v>
+        <v>1.145347362915935</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>0.02389581692904841</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.992051648802605</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.493935855031059</v>
+        <v>-4.435353783438996</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.189871494880445</v>
+        <v>1.21330432351727</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.1685679620287858</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.088943038423887</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.553810682388751</v>
+        <v>-4.495228610796688</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.151959055338793</v>
+        <v>1.175391883975619</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1086931346710937</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>3.039055633410698</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.467011184609742</v>
+        <v>-4.408429113017679</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.209079347772963</v>
+        <v>1.232512176409788</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1086931346710937</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>3.061456126733264</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.469480891071548</v>
+        <v>-4.410898819479485</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.208163866561653</v>
+        <v>1.231596695198478</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>0.1062234282092875</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>3.060046704229592</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.537851077395558</v>
+        <v>-4.479269005803495</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191822714506751</v>
+        <v>1.215255543143576</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.076619046126023</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.416434647769082</v>
+        <v>-4.357852576177018</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.230825994989233</v>
+        <v>1.254258823626058</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>3.067055754757914</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.447427807097787</v>
+        <v>-4.388845735505724</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.043138296298137</v>
+        <v>1.066571124934963</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.891765319798301</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.271953547305317</v>
+        <v>-4.213371475713254</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.117895232206913</v>
+        <v>1.141328060843738</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.896332551790089</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.382889799946566</v>
+        <v>-4.324307728354503</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.04926275991162</v>
+        <v>1.072695588548446</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1154991272455025</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.872074580551296</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.5859163774898</v>
+        <v>-4.527334305897736</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9711835141142329</v>
+        <v>0.9946163427510581</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.753390019245261</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.427990778554507</v>
+        <v>-4.369408706962443</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.044526140120482</v>
+        <v>1.067958968757308</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.763562405677394</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.341747315528129</v>
+        <v>-4.283165243936065</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073969795904894</v>
+        <v>1.097402624541719</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.0875274502977309</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.758508676251254</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.34293040017919</v>
+        <v>-4.284348328587127</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.065272337488995</v>
+        <v>1.08870516612582</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09317049876424244</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.746898622615873</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.219802693185107</v>
+        <v>-4.161220621593044</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.115075293319729</v>
+        <v>1.138508121956555</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09317049876424244</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.747450495648974</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.126992211734247</v>
+        <v>-4.068410140142184</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.081472177791439</v>
+        <v>1.104905006428264</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.0003600173133830875</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.732409476410856</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.078429159513218</v>
+        <v>-4.019847087921154</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.102770874604452</v>
+        <v>1.126203703241277</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>0.0482030349076471</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.763420783668075</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.965757941276967</v>
+        <v>-3.907175869684904</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.142915070410675</v>
+        <v>1.1663478990475</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1608742531438973</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.826099223121548</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.853380940094295</v>
+        <v>-3.794798868502232</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.193357166714411</v>
+        <v>1.216789995351236</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1608742531438973</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.831590518952215</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.051615508981025</v>
+        <v>-3.993033437388962</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.125560540928258</v>
+        <v>1.148993369565083</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.03736031574283327</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.724146979388716</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.134616790006304</v>
+        <v>-4.076034718414241</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9307157485187998</v>
+        <v>0.9541485771556251</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.551360168673065</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.975422517949728</v>
+        <v>-3.916840446357665</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.114543118060636</v>
+        <v>1.137975946697461</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.67150982939227</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.062021100930831</v>
+        <v>-4.003439029338768</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.094416710970517</v>
+        <v>1.117849539607343</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05593120027000703</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.686022855494593</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.02363743837268</v>
+        <v>-3.965055366780617</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.107189617336147</v>
+        <v>1.130622445972972</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01754753771185585</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.706472494371853</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.846521108337514</v>
+        <v>-3.787939036745451</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.174765178195515</v>
+        <v>1.198198006832341</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01754753771185585</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.703201523217154</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.816818984361221</v>
+        <v>-3.758236912769157</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.187329419547946</v>
+        <v>1.210762248184771</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.02201766292716922</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.70120283984988</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.637443563122453</v>
+        <v>-3.578861491530389</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.252866563349867</v>
+        <v>1.276299391986693</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.1347590952435495</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.789055870058725</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.682457776643059</v>
+        <v>-3.623875705050995</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.215668333273214</v>
+        <v>1.23910116191004</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>0.1044101999289448</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.751653988201552</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.949462286915495</v>
+        <v>-3.890880215323431</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.114558091503186</v>
+        <v>1.137990920140012</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.08995283811400373</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.640727727714729</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.23824950737441</v>
+        <v>-4.179667435782346</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9982471252161211</v>
+        <v>1.021679953852947</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1910389582130041</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.57927997755183</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.205773921203638</v>
+        <v>-4.147191849611573</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.008837321238747</v>
+        <v>1.032270149875572</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1910389582130041</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.576879939106147</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.18673579349634</v>
+        <v>-4.128153721904276</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.012977291529911</v>
+        <v>1.036410120166736</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2492225695441986</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.538494491515675</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.217862424646959</v>
+        <v>-4.159280353054895</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.178108508008344</v>
+        <v>1.201541336645169</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2492225695441986</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.716076360454355</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.27018280524775</v>
+        <v>-4.211600733655686</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.158013684754161</v>
+        <v>1.181446513390986</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2142757095353265</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.737877805445812</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.414505711172669</v>
+        <v>-4.355923639580605</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.106293052781119</v>
+        <v>1.129725881417945</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2142757095353265</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.743886335842738</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.266762740937667</v>
+        <v>-4.208180669345603</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.244542888667142</v>
+        <v>1.267975717303968</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.04646835230044333</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.92372339797569</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.368777423468888</v>
+        <v>-4.310195351876824</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.206530637186134</v>
+        <v>1.22996346582296</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.04646835230044333</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.926517019507171</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.232168079374795</v>
+        <v>-4.173586007782731</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.26183672321543</v>
+        <v>1.285269551852255</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>0.09014099179364915</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>3.009144974355285</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.374933412197445</v>
+        <v>-4.316351340605381</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.20381106682648</v>
+        <v>1.227243895463306</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.05262434102900126</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.922566251401805</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,45 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.574069546319763</v>
+        <v>3.867359061268421</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.312635413421323</v>
+        <v>-4.254053341829259</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.29506582013375</v>
+        <v>1.318498648770575</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.05262434102900126</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.988901805198626</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="2" t="n">
+        <v>45433</v>
+      </c>
+      <c r="B1971" t="n">
+        <v>3.593031824535461</v>
+      </c>
+      <c r="C1971" t="n">
+        <v>2.879379067861068</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>-4.254053341829259</v>
+      </c>
+      <c r="E1971" t="n">
+        <v>1.318498648770575</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>-0.05262434102900126</v>
+      </c>
+      <c r="G1971" t="n">
+        <v>2.872442864847436</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-31.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.7%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-687.0%</t>
+          <t>-687.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.5%</t>
+          <t>439.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.0%</t>
+          <t>-611.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-275.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-65.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-244.4%</t>
+          <t>-254.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-184.8%</t>
+          <t>-213.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-229.3%</t>
+          <t>-236.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-158.8%</t>
+          <t>-166.7%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.861090071840676</v>
+        <v>-0.8701886521770035</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.776536309276708</v>
+        <v>2.772896877142177</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.068655856232288</v>
+        <v>-1.077754436568615</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.691334791639304</v>
+        <v>2.687695359504773</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.486409879779125</v>
+        <v>-1.495508460115452</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.522160073725632</v>
+        <v>2.518520641591101</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.689699349100928</v>
+        <v>-1.698797929437255</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.440710502595833</v>
+        <v>2.437071070461302</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.897703407454005</v>
+        <v>-1.906801987790332</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.362401023808527</v>
+        <v>2.358761591673996</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.10911582834198</v>
+        <v>-2.118214408678307</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.272917511791325</v>
+        <v>2.269278079656794</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.448274205930502</v>
+        <v>-2.457372786266829</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.130338460062366</v>
+        <v>2.126699027927835</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.656764987382187</v>
+        <v>-2.665863567718514</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.06728043722046</v>
+        <v>2.063641005085929</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.903966172147408</v>
+        <v>-2.913064752483735</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97649871372294</v>
+        <v>1.972859281588409</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.396351200171505</v>
+        <v>-3.405449780507832</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.780651094557034</v>
+        <v>1.777011662422503</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.781531591101577</v>
+        <v>-3.790630171437904</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.625121476997868</v>
+        <v>1.621482044863337</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.12521436432824</v>
+        <v>-4.134312944664567</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.489417491161819</v>
+        <v>1.485778059027288</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.331726141215261</v>
+        <v>-4.340824721551589</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.402918839063268</v>
+        <v>1.399279406928737</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.587567226993954</v>
+        <v>-4.596665807330282</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.30235533145205</v>
+        <v>1.29871589931752</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.019373020143742</v>
+        <v>-5.028471600480069</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.11596590165954</v>
+        <v>1.112326469525009</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.254067014276294</v>
+        <v>-5.263165594612621</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.01037307900861</v>
+        <v>1.006733646874079</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.589729661506746</v>
+        <v>-5.598828241843074</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.874688611772394</v>
+        <v>0.871049179637863</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.95335590640706</v>
+        <v>-5.962454486743387</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7357256740465101</v>
+        <v>0.7320862419119791</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.318483289045806</v>
+        <v>-6.327581869382134</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5889292359968428</v>
+        <v>0.5852898038623118</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.727072066226485</v>
+        <v>-6.736170646562812</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.42425526913933</v>
+        <v>0.4206158370047994</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.003648166542318</v>
+        <v>-7.012746746878644</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3088102614844579</v>
+        <v>0.3051708293499273</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.420040040829315</v>
+        <v>-7.429138621165642</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1402475623785362</v>
+        <v>0.1366081302440056</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.79671705135916</v>
+        <v>-7.805815631695486</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0001645511647225817</v>
+        <v>-0.003803983299253133</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.142591873343969</v>
+        <v>-8.151690453680295</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1424149148129512</v>
+        <v>-0.1460543469474818</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.306171751528353</v>
+        <v>-8.31527033186468</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2094419460317041</v>
+        <v>-0.2130813781662346</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.602833093338552</v>
+        <v>-8.611931673674878</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3243275068265752</v>
+        <v>-0.3279669389611057</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.726077482553981</v>
+        <v>-8.735176062890307</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3776515670471499</v>
+        <v>-0.3812909991816804</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.109078871296612</v>
+        <v>-9.118177451632938</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5309542238657863</v>
+        <v>-0.5345936560003168</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.266477751509733</v>
+        <v>-9.275576331846059</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5913422599796045</v>
+        <v>-0.5949816921141351</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.626008074013734</v>
+        <v>-9.635106654350061</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7298040856831549</v>
+        <v>-0.7334435178176855</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.676357137467956</v>
+        <v>-9.685455717804283</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7420276911076664</v>
+        <v>-0.745667123242197</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.773976414889352</v>
+        <v>-9.783074995225679</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7780336514544559</v>
+        <v>-0.7816730835889865</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.770285489932942</v>
+        <v>-9.779384070269268</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7765572814718915</v>
+        <v>-0.7801967136064221</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.974543665262805</v>
+        <v>-9.983642245599132</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8527473544851949</v>
+        <v>-0.8563867866197254</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.19258143689398</v>
+        <v>-10.20168001723031</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9354799086532295</v>
+        <v>-0.93911934078776</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.11911160522653</v>
+        <v>-10.12821018556286</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8907202744928293</v>
+        <v>-0.8943597066273599</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.29423602261308</v>
+        <v>-10.3033346029494</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9462148206999297</v>
+        <v>-0.9498542528344602</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.52868811662757</v>
+        <v>-10.53778669696389</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.047214823207322</v>
+        <v>-1.050854255341852</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.81649196116481</v>
+        <v>-10.82559054150113</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.169008551796193</v>
+        <v>-1.172647983930724</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.86927811676513</v>
+        <v>-10.87837669710146</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.189007224197767</v>
+        <v>-1.192646656332298</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.05182354524566</v>
+        <v>-11.11040561683772</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.259331666960863</v>
+        <v>-1.282764495597688</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.575390372174662</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.99980803127684</v>
+        <v>-11.05839010286891</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.234535125686937</v>
+        <v>-1.257967954323762</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.579380707861062</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.14147987300096</v>
+        <v>-11.20006194459303</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.292679089275326</v>
+        <v>-1.316111917912152</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643939672127477</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.577905480962321</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.09188902857613</v>
+        <v>-11.15047110016819</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.257789341340521</v>
+        <v>-1.281222169977346</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.594348827702643</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.622713397782093</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.89273692133903</v>
+        <v>-10.95131899293109</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.191179632092364</v>
+        <v>-1.214612460729189</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.42902630175283</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.708855779705298</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.66689176861962</v>
+        <v>-10.72547384021168</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.091262497968391</v>
+        <v>-1.114695326605216</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.387099626165667</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.743590858093805</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.54231311228203</v>
+        <v>-10.60089518387409</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.040291890877296</v>
+        <v>-1.06372471951412</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.387099626165667</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.744730002649864</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.59520840032632</v>
+        <v>-10.65379047191838</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.058816231932902</v>
+        <v>-1.082249060569728</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.38214428007722</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.750336984465039</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.31129966939757</v>
+        <v>-10.36988174098963</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9395190353227667</v>
+        <v>-0.9629518639595913</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.38214428007722</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.756070688703676</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.23993327678792</v>
+        <v>-10.29851534837998</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9207097406727724</v>
+        <v>-0.9441425693095979</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.789153261875599</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.97609640958385</v>
+        <v>-10.03467848117591</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8250584751040524</v>
+        <v>-0.8484913037408774</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.779269780562692</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.708854608715452</v>
+        <v>-9.767436680307515</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7199963152560671</v>
+        <v>-0.7434291438928922</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.310777887467573</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.777435220063318</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.610947570038961</v>
+        <v>-9.669529641631025</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6811338147589314</v>
+        <v>-0.7045666433957569</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.242792137607016</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.817926355006191</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.586994029063003</v>
+        <v>-9.645576100655067</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6708838922230549</v>
+        <v>-0.6943167208598799</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.218838596631059</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.832966985737259</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.322934090740207</v>
+        <v>-9.38151616233227</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5785202330556882</v>
+        <v>-0.6019530616925133</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.954778658308262</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.978142632569185</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.615854467235369</v>
+        <v>-8.674436538827432</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2984754173140542</v>
+        <v>-0.3219082459508793</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.954778658308262</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.975355598908884</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.575670168869179</v>
+        <v>-8.634252240461242</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2820580740797367</v>
+        <v>-0.3054909027165618</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.914594359942072</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.99980980181644</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.495600373331374</v>
+        <v>-8.554182444923438</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2506633346438578</v>
+        <v>-0.2740961632806833</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.834524564404268</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.047218500359879</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.262119151101775</v>
+        <v>-8.320701222693838</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1493464169141658</v>
+        <v>-0.1727792455509909</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.601043342174669</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.19523166253549</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.112452760094261</v>
+        <v>-8.171034831686324</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09237207082411913</v>
+        <v>-0.1158048994609446</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.508139850932133</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.248081546968053</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.980177286463374</v>
+        <v>-8.038759358055437</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04409439462473763</v>
+        <v>-0.06752722326156269</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.375864377301247</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.322814317893612</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.789577611790222</v>
+        <v>-7.848159683382284</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03496053593216031</v>
+        <v>0.01152770729533525</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.185264702628094</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.43998918338514</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.540577813106641</v>
+        <v>-7.599159884698703</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1474667966292516</v>
+        <v>0.1240339679924265</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.185264702628094</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.452895524608799</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.646167802879745</v>
+        <v>-7.704749874471807</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.0227451288792091</v>
+        <v>-0.04617795751603415</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.290854692401198</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.261565601145718</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.664902704998342</v>
+        <v>-7.723484776590404</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01830525215043854</v>
+        <v>-0.005127576486386509</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.290854692401198</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.310109943022804</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.516962663590743</v>
+        <v>-7.575544735182805</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04239765397468931</v>
+        <v>-0.06583048261151436</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.270533776492641</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.202423569879771</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.49273402720177</v>
+        <v>-7.551316098793833</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04142018567257866</v>
+        <v>-0.06485301430940371</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.208246765459676</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.44918562043108</v>
+        <v>-7.507767692023142</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03096143505939564</v>
+        <v>-0.05439426369622069</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.201286153364583</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.207037226977222</v>
+        <v>-7.265619298569284</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08036027670329071</v>
+        <v>0.05692744806646566</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.215748507745726</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.143807855208873</v>
+        <v>-7.202389926800936</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1001841458698252</v>
+        <v>0.0767513172330001</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.246305140103668</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.210280628204921</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.020516720391742</v>
+        <v>-7.079098791983805</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1469986938072543</v>
+        <v>0.1235658651704292</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.123014005286538</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.281753403105776</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.999367521488299</v>
+        <v>-7.057949593080362</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1631593516059571</v>
+        <v>0.139726522969132</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.101864806383094</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.302143900685167</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.755602079504855</v>
+        <v>-6.814184151096917</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2564462367463851</v>
+        <v>0.2330134081095605</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.101864806383094</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.297924609032218</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.608705051786984</v>
+        <v>-6.667287123379047</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3173293617535498</v>
+        <v>0.2938965331167243</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.328643868139387</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.358854657837909</v>
+        <v>-6.417436729429973</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4100115943168814</v>
+        <v>0.3865787656800563</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.321385943123089</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.182962565370477</v>
+        <v>-6.241544636962541</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.483967554824503</v>
+        <v>0.460534726187678</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.054206564404506</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.324985066643738</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.011516102348014</v>
+        <v>-6.070098173940077</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.565873646088042</v>
+        <v>0.542440817451217</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8827601013820433</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.441180450511769</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.786483102679191</v>
+        <v>-5.845065174271254</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6549073235718685</v>
+        <v>0.631474494935043</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6577271017132205</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.57522072792936</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.722847360445257</v>
+        <v>-5.78142943203732</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6850564215197594</v>
+        <v>0.6616235928829344</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5940913594792859</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.618096974324038</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.629847319239358</v>
+        <v>-5.688429390831422</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7034506967859144</v>
+        <v>0.6800178681490889</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5940913594792859</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.599291233107834</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.389416822434498</v>
+        <v>-5.447998894026561</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8013659721327357</v>
+        <v>0.7779331434959107</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3536608626744256</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.745292607815627</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.317174254263303</v>
+        <v>-5.375756325855367</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8341923132360338</v>
+        <v>0.8107594845992088</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3536608626744256</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.749221921650447</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.201234404638118</v>
+        <v>-5.259816476230181</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8812468370034483</v>
+        <v>0.8578140083666228</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2768391316583018</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.795993544177462</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.092429519158391</v>
+        <v>-5.151011590750454</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9217668624153323</v>
+        <v>0.8983340337785073</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2768391316583018</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.792991615397455</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.87240872112138</v>
+        <v>-4.930990792713444</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.011354218640751</v>
+        <v>0.9879213900039254</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1356192865903215</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.879302559448857</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.739541032058103</v>
+        <v>-4.798123103650166</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.080395477067885</v>
+        <v>1.05696264843106</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1356192865903215</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.895196742250681</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.580025928538733</v>
+        <v>-4.638608000130796</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.145347362915935</v>
+        <v>1.12191453427911</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.02389581692904841</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.992051648802605</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.435353783438996</v>
+        <v>-4.493935855031059</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.21330432351727</v>
+        <v>1.189871494880445</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1685679620287858</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.088943038423887</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.495228610796688</v>
+        <v>-4.553810682388751</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.175391883975619</v>
+        <v>1.151959055338793</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1086931346710937</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.039055633410698</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.408429113017679</v>
+        <v>-4.467011184609742</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.232512176409788</v>
+        <v>1.209079347772963</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1086931346710937</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.061456126733264</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.410898819479485</v>
+        <v>-4.469480891071548</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.231596695198478</v>
+        <v>1.208163866561653</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1062234282092875</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.060046704229592</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.479269005803495</v>
+        <v>-4.537851077395558</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.215255543143576</v>
+        <v>1.191822714506751</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.076619046126023</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.357852576177018</v>
+        <v>-4.416434647769082</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254258823626058</v>
+        <v>1.230825994989233</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.067055754757914</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.388845735505724</v>
+        <v>-4.447427807097787</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.066571124934963</v>
+        <v>1.043138296298137</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.891765319798301</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.213371475713254</v>
+        <v>-4.271953547305317</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.141328060843738</v>
+        <v>1.117895232206913</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.896332551790089</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.324307728354503</v>
+        <v>-4.382889799946566</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.072695588548446</v>
+        <v>1.04926275991162</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1154991272455025</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.872074580551296</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.527334305897736</v>
+        <v>-4.5859163774898</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9946163427510581</v>
+        <v>0.9711835141142329</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.753390019245261</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.369408706962443</v>
+        <v>-4.427990778554507</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.067958968757308</v>
+        <v>1.044526140120482</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.763562405677394</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.283165243936065</v>
+        <v>-4.341747315528129</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.097402624541719</v>
+        <v>1.073969795904894</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.0875274502977309</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.758508676251254</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.284348328587127</v>
+        <v>-4.34293040017919</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.08870516612582</v>
+        <v>1.065272337488995</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.09317049876424244</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.746898622615873</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.161220621593044</v>
+        <v>-4.219802693185107</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.138508121956555</v>
+        <v>1.115075293319729</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.09317049876424244</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.747450495648974</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.068410140142184</v>
+        <v>-4.126992211734247</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.104905006428264</v>
+        <v>1.081472177791439</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.0003600173133830875</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.732409476410856</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.019847087921154</v>
+        <v>-4.078429159513218</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.126203703241277</v>
+        <v>1.102770874604452</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.0482030349076471</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.763420783668075</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942737</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.907175869684904</v>
+        <v>-3.965757941276967</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.1663478990475</v>
+        <v>1.142915070410675</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1608742531438973</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.826099223121548</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.794798868502232</v>
+        <v>-4.041924010305046</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.216789995351236</v>
+        <v>1.117939938630111</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1608742531438973</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.831590518952215</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.993033437388962</v>
+        <v>-4.240158579191776</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.148993369565083</v>
+        <v>1.050143312843958</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.03736031574283327</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.724146979388716</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.076034718414241</v>
+        <v>-4.323159860217055</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9541485771556251</v>
+        <v>0.8552985204344994</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.551360168673065</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.916840446357665</v>
+        <v>-4.16396558816048</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.137975946697461</v>
+        <v>1.039125889976335</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.67150982939227</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.003439029338768</v>
+        <v>-4.250564171141582</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.117849539607343</v>
+        <v>1.018999482886217</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.05593120027000703</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.686022855494593</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.965055366780617</v>
+        <v>-4.212180508583431</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.130622445972972</v>
+        <v>1.031772389251846</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01754753771185585</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.706472494371853</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.787939036745451</v>
+        <v>-4.035064178548265</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.198198006832341</v>
+        <v>1.099347950111214</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01754753771185585</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.703201523217154</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.758236912769157</v>
+        <v>-4.005362054571972</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.210762248184771</v>
+        <v>1.111912191463645</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.02201766292716922</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.70120283984988</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.578861491530389</v>
+        <v>-3.825986633333204</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.276299391986693</v>
+        <v>1.177449335265567</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1347590952435495</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.789055870058725</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.623875705050995</v>
+        <v>-3.87100084685381</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.23910116191004</v>
+        <v>1.140251105188914</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1044101999289448</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.751653988201552</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.890880215323431</v>
+        <v>-4.138005357126246</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.137990920140012</v>
+        <v>1.039140863418885</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08995283811400373</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.640727727714729</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.179667435782346</v>
+        <v>-4.426792577585161</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.021679953852947</v>
+        <v>0.9228298971318207</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1910389582130041</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.57927997755183</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.147191849611573</v>
+        <v>-4.394316991414389</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.032270149875572</v>
+        <v>0.9334200931544463</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1910389582130041</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.576879939106147</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.128153721904276</v>
+        <v>-4.375278863707091</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.036410120166736</v>
+        <v>0.93756006344561</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2492225695441986</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.538494491515675</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.159280353054895</v>
+        <v>-4.40640549485771</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201541336645169</v>
+        <v>1.102691279924043</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2492225695441986</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.716076360454355</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.211600733655686</v>
+        <v>-4.458725875458502</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.181446513390986</v>
+        <v>1.08259645666986</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2142757095353265</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.737877805445812</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.355923639580605</v>
+        <v>-4.60304878138342</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.129725881417945</v>
+        <v>1.030875824696819</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2142757095353265</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.743886335842738</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.208180669345603</v>
+        <v>-4.455305811148418</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.267975717303968</v>
+        <v>1.169125660582842</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.04646835230044333</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.92372339797569</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.310195351876824</v>
+        <v>-4.557320493679639</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.22996346582296</v>
+        <v>1.131113409101834</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.04646835230044333</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.926517019507171</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864729</v>
+        <v>3.805605409864731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.173586007782731</v>
+        <v>-4.420711149585546</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.285269551852255</v>
+        <v>1.186419495131129</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.09014099179364915</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.009144974355285</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>3.798236219360614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.316351340605381</v>
+        <v>-4.563476482408197</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.227243895463306</v>
+        <v>1.12839383874218</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.05262434102900126</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.922566251401805</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268421</v>
+        <v>3.867359061268424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.254053341829259</v>
+        <v>-4.501178483632074</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.318498648770575</v>
+        <v>1.219648592049449</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.05262434102900126</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.988901805198626</v>
+        <v>2.94770342209875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.593031824535461</v>
+        <v>3.467438967008829</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.879379067861068</v>
+        <v>2.800568242372762</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.254053341829259</v>
+        <v>-4.501178483632074</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.318498648770575</v>
+        <v>1.219648592049449</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.05262434102900126</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.872442864847436</v>
+        <v>2.793632039359129</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-687.9%</t>
+          <t>-658.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.7%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.7%</t>
+          <t>-570.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.5%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-254.3%</t>
+          <t>-237.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-285.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>-83.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.1%</t>
+          <t>-239.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-171.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-152.4%</t>
         </is>
       </c>
     </row>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8701886521770035</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.772896877142177</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.077754436568615</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.687695359504773</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.495508460115452</v>
+        <v>-1.199905620109299</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.518520641591101</v>
+        <v>2.636761777593562</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>1.022526831340739</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.730596548755473</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.698797929437255</v>
+        <v>-1.403195089431102</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.437071070461302</v>
+        <v>2.555312206463763</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9899765505255895</v>
+        <v>1.060606242106311</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.710932596865305</v>
+        <v>3.753310411813738</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.906801987790332</v>
+        <v>-1.611199147784179</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.358761591673996</v>
+        <v>2.477002727676457</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9899765505255895</v>
+        <v>1.060606242106311</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.71582474141923</v>
+        <v>3.758202556367663</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.118214408678307</v>
+        <v>-1.822611568672154</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.269278079656794</v>
+        <v>2.387519215659256</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7785641296376145</v>
+        <v>0.8491938212183361</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.584058745224433</v>
+        <v>3.626436560172866</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.457372786266829</v>
+        <v>-2.161769946260677</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.126699027927835</v>
+        <v>2.244940163930296</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4394057520490924</v>
+        <v>0.510035443629814</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.373648017977769</v>
+        <v>3.416025832926202</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.665863567718514</v>
+        <v>-2.370260727712361</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.063641005085929</v>
+        <v>2.18188214108839</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.230914970597408</v>
+        <v>0.3015446621781296</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.268891838845527</v>
+        <v>3.31126965379396</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.913064752483735</v>
+        <v>-2.617461912477583</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.972859281588409</v>
+        <v>2.09110041759087</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2510683240962204</v>
+        <v>0.321698015676942</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.289082601353383</v>
+        <v>3.331460416301816</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.405449780507832</v>
+        <v>-3.10984694050168</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.777011662422503</v>
+        <v>1.895252798424963</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.1706870123471547</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.994757976582657</v>
+        <v>3.03713579153109</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.790630171437904</v>
+        <v>-3.495027331431752</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.621482044863337</v>
+        <v>1.739723180865798</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.1706870123471547</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.993300515395521</v>
+        <v>3.035678330343953</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.134312944664567</v>
+        <v>-3.838710104658415</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.485778059027288</v>
+        <v>1.604019195029749</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3492227559550946</v>
+        <v>-0.2785930643743729</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.930326007633806</v>
+        <v>2.972703822582238</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.340824721551589</v>
+        <v>-4.045221881545436</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.399279406928737</v>
+        <v>1.517520542931198</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.4851048412613944</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.802525000157851</v>
+        <v>2.844902815106284</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.596665807330282</v>
+        <v>-4.301062967324129</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.29871589931752</v>
+        <v>1.416957035319981</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.4851048412613944</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.80429792685811</v>
+        <v>2.846675741806543</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.028471600480069</v>
+        <v>-4.732868760473917</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.112326469525009</v>
+        <v>1.23056760552747</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.692152029283383</v>
+        <v>-0.6215223377026614</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.708780316460754</v>
+        <v>2.751158131409187</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.263165594612621</v>
+        <v>-4.967562754606469</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.006733646874079</v>
+        <v>1.12497478287654</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.6151860704734062</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700866851800398</v>
+        <v>2.743244666748831</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.598828241843074</v>
+        <v>-5.303225401836921</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.871049179637863</v>
+        <v>0.9892903156403237</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.6151860704734062</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699447443456363</v>
+        <v>2.741825258404796</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.962454486743387</v>
+        <v>-5.666851646737235</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7320862419119791</v>
+        <v>0.8503273779144402</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.713407707340532</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.689379836518762</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.327581869382134</v>
+        <v>-6.031979029375981</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5852898038623118</v>
+        <v>0.7035309398647729</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-1.009718491639545</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.510847880945186</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.736170646562812</v>
+        <v>-6.440567806556659</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4206158370047994</v>
+        <v>0.5388569730072605</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.264456158651538</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.012746746878644</v>
+        <v>-6.717143906872492</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3051708293499273</v>
+        <v>0.423411965352388</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.259641591122999</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.429138621165642</v>
+        <v>-7.133535781159489</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1366081302440056</v>
+        <v>0.2548492662464668</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.257635641731876</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.805815631695486</v>
+        <v>-7.510212791689334</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.003803983299253133</v>
+        <v>0.114437152703208</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.267894332400555</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.151690453680295</v>
+        <v>-7.856087613674143</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1460543469474818</v>
+        <v>-0.02781321094502065</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.26399389754625</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.31527033186468</v>
+        <v>-8.019667491858527</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2130813781662346</v>
+        <v>-0.09484024216377351</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.418307268820223</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.262398817601251</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.611931673674878</v>
+        <v>-8.316328833668726</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3279669389611057</v>
+        <v>-0.2097258029586446</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.487050404554102</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.224931912090132</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.735176062890307</v>
+        <v>-8.439573222884155</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3812909991816804</v>
+        <v>-0.2630498631792193</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.487050404554102</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.220905607555729</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.118177451632938</v>
+        <v>-8.822574611626786</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5345936560003168</v>
+        <v>-0.4163525199978562</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.487050404554102</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.220803506234145</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.275576331846059</v>
+        <v>-8.979973491839907</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5949816921141351</v>
+        <v>-0.476740556111674</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.644449284767223</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.128935694077703</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.635106654350061</v>
+        <v>-9.339503814343908</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7334435178176855</v>
+        <v>-0.6152023818152248</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.644449284767223</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.134285997375753</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.685455717804283</v>
+        <v>-9.38985287779813</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.745667123242197</v>
+        <v>-0.6274259872397359</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.694798348221445</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.111992579260397</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.783074995225679</v>
+        <v>-9.487472155219526</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7816730835889865</v>
+        <v>-0.6634319475865254</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.792417625642841</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.014084948480895</v>
+        <v>2.056462763429328</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.779384070269268</v>
+        <v>-9.483781230263116</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7801967136064221</v>
+        <v>-0.6619555776039614</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.792417625642841</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.014084948480895</v>
+        <v>2.056462763429328</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.983642245599132</v>
+        <v>-9.688039405592979</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8563867866197254</v>
+        <v>-0.7381456506172643</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.990686261837552</v>
+        <v>-1.92005657025683</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.943014778831144</v>
+        <v>1.985392593779577</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.20168001723031</v>
+        <v>-9.906077177224157</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.93911934078776</v>
+        <v>-0.8208782047852994</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.165457029933451</v>
+        <v>-2.094827338352729</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.842634872458041</v>
+        <v>1.885012687406473</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.12821018556286</v>
+        <v>-9.832607345556708</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8943597066273599</v>
+        <v>-0.7761185706248988</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.091987198266002</v>
+        <v>-2.021357506685281</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.902088472951931</v>
+        <v>1.944466287900364</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.3033346029494</v>
+        <v>-10.00773176294325</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9498542528344602</v>
+        <v>-0.8316131168319991</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.196481924071825</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.811569043267521</v>
+        <v>1.853946858215954</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.53778669696389</v>
+        <v>-10.24218385695774</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.050854255341852</v>
+        <v>-0.9326131193393912</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.196481924071825</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.804349878365925</v>
+        <v>1.846727693314358</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.82559054150113</v>
+        <v>-10.52998770149498</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.172647983930724</v>
+        <v>-1.054406847928262</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.554915460189784</v>
+        <v>-2.484285768609063</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.624995380869606</v>
+        <v>1.667373195818039</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.87837669710146</v>
+        <v>-10.58277385709531</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.192646656332298</v>
+        <v>-1.074405520329837</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.650590946772181</v>
+        <v>-2.57996125519146</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.568705878758724</v>
+        <v>1.611083693707157</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.11040561683772</v>
+        <v>-10.81480277683157</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.282764495597688</v>
+        <v>-1.164523359595227</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.641973952379883</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.576569804023218</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05839010286891</v>
+        <v>-10.76278726286276</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.257967954323762</v>
+        <v>-1.139726818321301</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.641973952379883</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.580560139709619</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.20006194459303</v>
+        <v>-10.90445910458688</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.316111917912152</v>
+        <v>-1.197870781909691</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.641973952379883</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.579084912810877</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.15047110016819</v>
+        <v>-10.85486826016204</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.281222169977346</v>
+        <v>-1.162981033974885</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.592383107955049</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.62389282963065</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.95131899293109</v>
+        <v>-10.65571615292494</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.214612460729189</v>
+        <v>-1.096371324726728</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.427060582005236</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.710035211553855</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.72547384021168</v>
+        <v>-10.42987100020553</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.114695326605216</v>
+        <v>-0.9964541906027544</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.385133906418072</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.744770289942362</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.60089518387409</v>
+        <v>-10.30529234386794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.06372471951412</v>
+        <v>-0.9454835835116593</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.385133906418072</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.745909434498421</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.65379047191838</v>
+        <v>-10.35818763191222</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.082249060569728</v>
+        <v>-0.9640079245672659</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.380178560329626</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.751516416313596</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.36988174098963</v>
+        <v>-10.07427890098348</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9629518639595913</v>
+        <v>-0.8447107279571302</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.380178560329626</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.757250120552232</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.29851534837998</v>
+        <v>-10.00291250837383</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9441425693095979</v>
+        <v>-0.8259014333071364</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.308812167719978</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.790332693724156</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03467848117591</v>
+        <v>-9.739075641169759</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8484913037408774</v>
+        <v>-0.7302501677384159</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.308812167719978</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.780449212411248</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.767436680307515</v>
+        <v>-9.471833840301361</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7434291438928922</v>
+        <v>-0.6251880078904306</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.308812167719978</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.778614651911874</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.669529641631025</v>
+        <v>-9.37392680162487</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7045666433957569</v>
+        <v>-0.5863255073932954</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.240826417859422</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.819105786854748</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.645576100655067</v>
+        <v>-9.349973260648913</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6943167208598799</v>
+        <v>-0.5760755848574184</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.216872876883464</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.834146417585816</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.38151616233227</v>
+        <v>-9.085913322326116</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6019530616925133</v>
+        <v>-0.4837119256900517</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.952812938560668</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.979322064417741</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.674436538827432</v>
+        <v>-8.378833698821278</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3219082459508793</v>
+        <v>-0.2036671099484177</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.952812938560668</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.97653503075744</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.634252240461242</v>
+        <v>-8.338649400455088</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3054909027165618</v>
+        <v>-0.1872497667141002</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-1.912628640194478</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>2.000989233664996</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.554182444923438</v>
+        <v>-8.258579604917283</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2740961632806833</v>
+        <v>-0.1558550272782213</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.832558844656674</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>2.048397932208435</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.320701222693838</v>
+        <v>-8.025098382687684</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1727792455509909</v>
+        <v>-0.05453810954852933</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.599077622427075</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.196411094384047</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.171034831686324</v>
+        <v>-7.875431991680169</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1158048994609446</v>
+        <v>0.002436236541517367</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.506174131184539</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.249260978816609</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.038759358055437</v>
+        <v>-7.743156518049283</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06752722326156269</v>
+        <v>0.05071391274089931</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.373898657553652</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.323993749742169</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.848159683382284</v>
+        <v>-7.55255684337613</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01152770729533525</v>
+        <v>0.1297688432977968</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.1832989828805</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.441168615233697</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.599159884698703</v>
+        <v>-7.303557044692549</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1240339679924265</v>
+        <v>0.2422751039948881</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.1832989828805</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.454074956457355</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.704749874471807</v>
+        <v>-7.409147034465653</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04617795751603415</v>
+        <v>0.0720631784864274</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.288888972653604</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.262745032994274</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.723484776590404</v>
+        <v>-7.42788193658425</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.005127576486386509</v>
+        <v>0.113113559516075</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.288888972653604</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.311289374871361</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.575544735182805</v>
+        <v>-7.279941895176651</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.06583048261151436</v>
+        <v>0.05241065339094719</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.268568056745046</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.203603001728327</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.551316098793833</v>
+        <v>-7.255713258787678</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06485301430940371</v>
+        <v>0.05338812169305829</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.244339420356074</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.209426197308233</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.507767692023142</v>
+        <v>-7.212164852016988</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05439426369622069</v>
+        <v>0.06384687230624131</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.244339420356074</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.202465585213139</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.265619298569284</v>
+        <v>-6.97001645856313</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05692744806646566</v>
+        <v>0.1751685840689277</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.244339420356074</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.216927939594282</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.202389926800936</v>
+        <v>-6.906787086794782</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0767513172330001</v>
+        <v>0.1949924532354617</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.244339420356074</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.211460060053478</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.079098791983805</v>
+        <v>-6.783495951977651</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1235658651704292</v>
+        <v>0.2418070011728912</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.121048285538944</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.282932834954333</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.057949593080362</v>
+        <v>-6.762346753074207</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.139726522969132</v>
+        <v>0.2579676589715936</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.0998990866355</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.303323332533724</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.814184151096917</v>
+        <v>-6.518581311090763</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2330134081095605</v>
+        <v>0.3512545441120221</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.0998990866355</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.299104040880775</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.667287123379047</v>
+        <v>-6.371684283372893</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2938965331167243</v>
+        <v>0.4121376691191858</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.052240844656912</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.329823299987944</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.417436729429973</v>
+        <v>-6.121833889423819</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3865787656800563</v>
+        <v>0.5048199016825179</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.052240844656912</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.322565374971646</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.241544636962541</v>
+        <v>-5.945941796956387</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.460534726187678</v>
+        <v>0.5787758621901395</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.052240844656912</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.326164498492294</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.070098173940077</v>
+        <v>-5.774495333933923</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.542440817451217</v>
+        <v>0.6606819534536785</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-0.8807943816344491</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.442359882360326</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.845065174271254</v>
+        <v>-5.5494623342651</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.631474494935043</v>
+        <v>0.7497156309375046</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.6557613819656263</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.576400159777917</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.78142943203732</v>
+        <v>-5.485826592031166</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6616235928829344</v>
+        <v>0.7798647288853959</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5921256397316917</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.619276406172595</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.688429390831422</v>
+        <v>-5.392826550825268</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6800178681490889</v>
+        <v>0.7982590041515509</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.5921256397316917</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.60047066495639</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.447998894026561</v>
+        <v>-5.152396054020407</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7779331434959107</v>
+        <v>0.8961742794983723</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3516951429268315</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.746472039664184</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.375756325855367</v>
+        <v>-5.080153485849213</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8107594845992088</v>
+        <v>0.9290006206016703</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.3516951429268315</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.750401353499004</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.259816476230181</v>
+        <v>-4.964213636224027</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8578140083666228</v>
+        <v>0.9760551443690844</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2748734119107076</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.797172976026018</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.151011590750454</v>
+        <v>-4.8554087507443</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8983340337785073</v>
+        <v>1.016575169780969</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.2748734119107076</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.794171047246012</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.930990792713444</v>
+        <v>-4.63538795270729</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9879213900039254</v>
+        <v>1.106162526006387</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1336535668427273</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.880481991297414</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.798123103650166</v>
+        <v>-4.502520263644012</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.05696264843106</v>
+        <v>1.175203784433521</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1336535668427273</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.896376174099237</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.638608000130796</v>
+        <v>-4.343005160124642</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.12191453427911</v>
+        <v>1.240155670281571</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>0.02586153667664259</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.993231080651161</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.493935855031059</v>
+        <v>-4.198333015024905</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.189871494880445</v>
+        <v>1.308112630882906</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.17053368177638</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.090122470272444</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.553810682388751</v>
+        <v>-4.258207842382597</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.151959055338793</v>
+        <v>1.270200191341255</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1106588544186879</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>3.040235065259254</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.467011184609742</v>
+        <v>-4.171408344603588</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.209079347772963</v>
+        <v>1.327320483775425</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.1106588544186879</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>3.06263555858182</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.469480891071548</v>
+        <v>-4.173878051065394</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.208163866561653</v>
+        <v>1.326405002564115</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>0.1081891479568817</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>3.061226136078149</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.537851077395558</v>
+        <v>-4.242248237389404</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191822714506751</v>
+        <v>1.310063850509212</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1174648469930967</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.07779847797458</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.416434647769082</v>
+        <v>-4.120831807762928</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.230825994989233</v>
+        <v>1.349067130991694</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1174648469930967</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>3.068235186606471</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.447427807097787</v>
+        <v>-4.151824967091633</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.043138296298137</v>
+        <v>1.161379432300599</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1174648469930967</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.892944751646858</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.271953547305317</v>
+        <v>-3.976350707299164</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.117895232206913</v>
+        <v>1.236136368209374</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1174648469930967</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.897511983638645</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.382889799946566</v>
+        <v>-4.087286959940412</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.04926275991162</v>
+        <v>1.167503895914082</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.1174648469930967</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.873254012399852</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.5859163774898</v>
+        <v>-4.290313537483645</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9711835141142329</v>
+        <v>1.089424650116694</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.08556173055013672</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.754569451093818</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.427990778554507</v>
+        <v>-4.132387938548352</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.044526140120482</v>
+        <v>1.162767276122944</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.08556173055013672</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.76474183752595</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.341747315528129</v>
+        <v>-4.046144475521975</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073969795904894</v>
+        <v>1.192210931907355</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.08556173055013672</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.759688108099811</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.34293040017919</v>
+        <v>-4.047327560173036</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.065272337488995</v>
+        <v>1.183513473491456</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09120477901664825</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.748078054464429</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.219802693185107</v>
+        <v>-3.924199853178953</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.115075293319729</v>
+        <v>1.233316429322191</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.09120477901664825</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.748629927497531</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.126992211734247</v>
+        <v>-3.831389371728094</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.081472177791439</v>
+        <v>1.1997133137939</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>0.001605702434211098</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.733588908259412</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.078429159513218</v>
+        <v>-3.782826319507063</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.102770874604452</v>
+        <v>1.221012010606914</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>0.05016875465524129</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.764600215516631</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.965757941276967</v>
+        <v>-3.670155101270813</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.142915070410675</v>
+        <v>1.261156206413137</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1628399728914915</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.827278654970104</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268536</v>
+        <v>3.743044028268533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.041924010305046</v>
+        <v>-3.557778100088141</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117939938630111</v>
+        <v>1.311598302716873</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.1628399728914915</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.832769950800771</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.240158579191776</v>
+        <v>-3.756012668974871</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.050143312843958</v>
+        <v>1.24380167693072</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.03539459599523909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.725326411237272</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.323159860217055</v>
+        <v>-3.83901395000015</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8552985204344994</v>
+        <v>1.048956884521261</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05396548052241285</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.552539600521621</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.16396558816048</v>
+        <v>-3.679819677943574</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.039125889976335</v>
+        <v>1.232784254063098</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05396548052241285</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.672689261240827</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.250564171141582</v>
+        <v>-3.766418260924677</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.018999482886217</v>
+        <v>1.212657846972979</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.05396548052241285</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.68720228734315</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.74117049438342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.212180508583431</v>
+        <v>-3.728034598366526</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.031772389251846</v>
+        <v>1.225430753338608</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01558181796426167</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.707651926220409</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.035064178548265</v>
+        <v>-3.55091826833136</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.099347950111214</v>
+        <v>1.293006314197977</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.01558181796426167</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.704380955065711</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.005362054571972</v>
+        <v>-3.521216144355066</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.111912191463645</v>
+        <v>1.305570555550407</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.02005194317957504</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.702382271698436</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.825986633333204</v>
+        <v>-3.341840723116298</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.177449335265567</v>
+        <v>1.371107699352329</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.1367248149911436</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.790235301907282</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.87100084685381</v>
+        <v>-3.386854936636904</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.140251105188914</v>
+        <v>1.333909469275676</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>0.106375919676539</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.752833420050109</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.138005357126246</v>
+        <v>-3.65385944690934</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.039140863418885</v>
+        <v>1.232799227505648</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.08798711836640954</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.641907159563285</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.426792577585161</v>
+        <v>-3.942646667368255</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9228298971318207</v>
+        <v>1.116488261218583</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1890732384654099</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.580459409400387</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.394316991414389</v>
+        <v>-3.910171081197483</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9334200931544463</v>
+        <v>1.127078457241209</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.1890732384654099</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.578059370954703</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.375278863707091</v>
+        <v>-3.891132953490185</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.93756006344561</v>
+        <v>1.131218427532373</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2472568497966044</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.539673923364231</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601252</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.40640549485771</v>
+        <v>-3.922259584640803</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.102691279924043</v>
+        <v>1.296349644010806</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.2472568497966044</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.717255792302912</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.458725875458502</v>
+        <v>-4.044171958305161</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.08259645666986</v>
+        <v>1.248418023531196</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3204835234030043</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.674153117125206</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.60304878138342</v>
+        <v>-4.18849486423008</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.030875824696819</v>
+        <v>1.196697391558155</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3204835234030043</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.680161647522132</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.455305811148418</v>
+        <v>-4.040751893995077</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.169125660582842</v>
+        <v>1.334947227444178</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1526761661681211</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.859998709655084</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651171</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.557320493679639</v>
+        <v>-4.142766576526299</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.131113409101834</v>
+        <v>1.29693497596317</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1526761661681211</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.862792331186565</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864731</v>
+        <v>3.805605409864727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.420711149585546</v>
+        <v>-4.006157232432207</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.186419495131129</v>
+        <v>1.352241061992465</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>-0.01606682207402865</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.945420286034679</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360614</v>
+        <v>3.798236219360611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.563476482408197</v>
+        <v>-4.148922565254857</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.12839383874218</v>
+        <v>1.294215405603516</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1588321548966791</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.858841563081199</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268424</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.501178483632074</v>
+        <v>-4.086624566478735</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.219648592049449</v>
+        <v>1.385470158910785</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1588321548966791</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.925177116878019</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.467438967008829</v>
+        <v>3.667501561709265</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.800568242372762</v>
+        <v>2.943287536270443</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.501178483632074</v>
+        <v>-4.086624566478735</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.219648592049449</v>
+        <v>1.385470158910785</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1588321548966791</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.793632039359129</v>
+        <v>2.936351333256811</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-6.1%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-658.3%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.2%</t>
+          <t>-568.9%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-237.7%</t>
+          <t>-237.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-285.5%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-83.5%</t>
+          <t>-716.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-204.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-239.9%</t>
+          <t>-239.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-171.7%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-141.2%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.199905620109299</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.636761777593562</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.022526831340739</v>
+        <v>0.9518971397600179</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.730596548755473</v>
+        <v>3.68821873380704</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.403195089431102</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.555312206463763</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.060606242106311</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.753310411813738</v>
+        <v>3.710932596865305</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.611199147784179</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.477002727676457</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.060606242106311</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.758202556367663</v>
+        <v>3.71582474141923</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.822611568672154</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.387519215659256</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8491938212183361</v>
+        <v>0.7785641296376145</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.626436560172866</v>
+        <v>3.584058745224433</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.161769946260677</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.244940163930296</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.510035443629814</v>
+        <v>0.4394057520490924</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.416025832926202</v>
+        <v>3.373648017977769</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.370260727712361</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.18188214108839</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3015446621781296</v>
+        <v>0.230914970597408</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31126965379396</v>
+        <v>3.268891838845527</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.617461912477583</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.09110041759087</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.321698015676942</v>
+        <v>0.2510683240962204</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.331460416301816</v>
+        <v>3.289082601353383</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.10984694050168</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.895252798424963</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1706870123471547</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.03713579153109</v>
+        <v>2.994757976582657</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.495027331431752</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.739723180865798</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1706870123471547</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.035678330343953</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.838710104658415</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.604019195029749</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2785930643743729</v>
+        <v>-0.3492227559550946</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.972703822582238</v>
+        <v>2.930326007633806</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.045221881545436</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.517520542931198</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4851048412613944</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.844902815106284</v>
+        <v>2.802525000157851</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.301062967324129</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.416957035319981</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4851048412613944</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.846675741806543</v>
+        <v>2.80429792685811</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.732868760473917</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.23056760552747</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6215223377026614</v>
+        <v>-0.692152029283383</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.751158131409187</v>
+        <v>2.708780316460754</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.967562754606469</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.12497478287654</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6151860704734062</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.743244666748831</v>
+        <v>2.700866851800398</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.303225401836921</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9892903156403237</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6151860704734062</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.741825258404796</v>
+        <v>2.699447443456363</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.666851646737235</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8503273779144402</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.713407707340532</v>
+        <v>-0.7840373989212537</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.689379836518762</v>
+        <v>2.647002021570329</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.031979029375981</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7035309398647729</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.009718491639545</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.510847880945186</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.440567806556659</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5388569730072605</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.264456158651538</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.717143906872492</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.423411965352388</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.259641591122999</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.133535781159489</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2548492662464668</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.257635641731876</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.510212791689334</v>
+        <v>-7.580842483270056</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.114437152703208</v>
+        <v>0.08618527607091897</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.267894332400555</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.856087613674143</v>
+        <v>-7.926717305254865</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02781321094502065</v>
+        <v>-0.05606508757730966</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.26399389754625</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.019667491858527</v>
+        <v>-8.090297183439249</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09484024216377351</v>
+        <v>-0.1230921187960621</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.418307268820223</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.262398817601251</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.316328833668726</v>
+        <v>-8.386958525249447</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2097258029586446</v>
+        <v>-0.2379776795909332</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.487050404554102</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.224931912090132</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.439573222884155</v>
+        <v>-8.510202914464877</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2630498631792193</v>
+        <v>-0.2913017398115083</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.487050404554102</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.220905607555729</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.822574611626786</v>
+        <v>-8.893204303207508</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4163525199978562</v>
+        <v>-0.4446043966301447</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.487050404554102</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.220803506234145</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.979973491839907</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.476740556111674</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.644449284767223</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.128935694077703</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.339503814343908</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6152023818152248</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.644449284767223</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.134285997375753</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.38985287779813</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6274259872397359</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.694798348221445</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.111992579260397</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.487472155219526</v>
+        <v>-9.558101846800248</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6634319475865254</v>
+        <v>-0.6916838242188144</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.792417625642841</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.056462763429328</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.483781230263116</v>
+        <v>-9.554410921843838</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6619555776039614</v>
+        <v>-0.69020745423625</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.792417625642841</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.056462763429328</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.688039405592979</v>
+        <v>-9.758669097173701</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7381456506172643</v>
+        <v>-0.7663975272495529</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.92005657025683</v>
+        <v>-1.990686261837552</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.985392593779577</v>
+        <v>1.943014778831144</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.906077177224157</v>
+        <v>-9.976706868804879</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8208782047852994</v>
+        <v>-0.8491300814175879</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.094827338352729</v>
+        <v>-2.165457029933451</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.885012687406473</v>
+        <v>1.842634872458041</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.832607345556708</v>
+        <v>-9.90323703713743</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7761185706248988</v>
+        <v>-0.8043704472571873</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.021357506685281</v>
+        <v>-2.091987198266002</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.944466287900364</v>
+        <v>1.902088472951931</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.00773176294325</v>
+        <v>-10.07836145452397</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8316131168319991</v>
+        <v>-0.8598649934642877</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.196481924071825</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.853946858215954</v>
+        <v>1.811569043267521</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.24218385695774</v>
+        <v>-10.31281354853846</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9326131193393912</v>
+        <v>-0.9608649959716797</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.196481924071825</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.846727693314358</v>
+        <v>1.804349878365925</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.52998770149498</v>
+        <v>-10.6006173930757</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.054406847928262</v>
+        <v>-1.082658724560551</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.484285768609063</v>
+        <v>-2.554915460189784</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.667373195818039</v>
+        <v>1.624995380869606</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.58277385709531</v>
+        <v>-10.65340354867603</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.074405520329837</v>
+        <v>-1.102657396962126</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.57996125519146</v>
+        <v>-2.650590946772181</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.611083693707157</v>
+        <v>1.568705878758724</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.81480277683157</v>
+        <v>-10.88543246841229</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.164523359595227</v>
+        <v>-1.192775236227515</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.641973952379883</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.576569804023218</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.76278726286276</v>
+        <v>-10.83341695444348</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.139726818321301</v>
+        <v>-1.16797869495359</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.641973952379883</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.580560139709619</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.90445910458688</v>
+        <v>-10.9750887961676</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.197870781909691</v>
+        <v>-1.226122658541979</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.641973952379883</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.579084912810877</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.85486826016204</v>
+        <v>-10.92549795174276</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.162981033974885</v>
+        <v>-1.191232910607174</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.592383107955049</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.62389282963065</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.65571615292494</v>
+        <v>-10.72634584450566</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.096371324726728</v>
+        <v>-1.124623201359017</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.427060582005236</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.710035211553855</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.42987100020553</v>
+        <v>-10.50050069178625</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9964541906027544</v>
+        <v>-1.024706067235044</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.385133906418072</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.744770289942362</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.30529234386794</v>
+        <v>-10.37592203544866</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9454835835116593</v>
+        <v>-0.9737354601439487</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.385133906418072</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.745909434498421</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.35818763191222</v>
+        <v>-10.42881732349295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9640079245672659</v>
+        <v>-0.9922598011995554</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.380178560329626</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.751516416313596</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.07427890098348</v>
+        <v>-10.1449085925642</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8447107279571302</v>
+        <v>-0.8729626045894197</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.380178560329626</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.757250120552232</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.00291250837383</v>
+        <v>-10.07354219995455</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8259014333071364</v>
+        <v>-0.8541533099394254</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.308812167719978</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.790332693724156</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.739075641169759</v>
+        <v>-9.809705332750482</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7302501677384159</v>
+        <v>-0.7585020443707053</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.308812167719978</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.780449212411248</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.471833840301361</v>
+        <v>-9.542463531882085</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6251880078904306</v>
+        <v>-0.6534398845227201</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.308812167719978</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.778614651911874</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781942</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.37392680162487</v>
+        <v>-9.444556493205594</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5863255073932954</v>
+        <v>-0.6145773840255848</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.240826417859422</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.819105786854748</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.349973260648913</v>
+        <v>-9.420602952229636</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5760755848574184</v>
+        <v>-0.6043274614897078</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.216872876883464</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.834146417585816</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.085913322326116</v>
+        <v>-9.156543013906839</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4837119256900517</v>
+        <v>-0.5119638023223412</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.952812938560668</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.979322064417741</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.378833698821278</v>
+        <v>-8.449463390402002</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2036671099484177</v>
+        <v>-0.2319189865807072</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.952812938560668</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.97653503075744</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.338649400455088</v>
+        <v>-8.409279092035812</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1872497667141002</v>
+        <v>-0.2155016433463897</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.912628640194478</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.000989233664996</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.258579604917283</v>
+        <v>-8.329209296498007</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1558550272782213</v>
+        <v>-0.1841069039105108</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.832558844656674</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.048397932208435</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.025098382687684</v>
+        <v>-8.095728074268408</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05453810954852933</v>
+        <v>-0.08278998618081879</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.599077622427075</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.196411094384047</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.875431991680169</v>
+        <v>-7.946061683260893</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.002436236541517367</v>
+        <v>-0.02581564009077209</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.506174131184539</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.249260978816609</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.743156518049283</v>
+        <v>-7.813786209630006</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.05071391274089931</v>
+        <v>0.02246203610860986</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.373898657553652</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.323993749742169</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.55255684337613</v>
+        <v>-7.623186534956853</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1297688432977968</v>
+        <v>0.1015169666655074</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.1832989828805</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.441168615233697</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.303557044692549</v>
+        <v>-7.374186736273272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2422751039948881</v>
+        <v>0.2140232273625986</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.1832989828805</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.454074956457355</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.409147034465653</v>
+        <v>-7.479776726046377</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.0720631784864274</v>
+        <v>0.04381130185413795</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.288888972653604</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.262745032994274</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.42788193658425</v>
+        <v>-7.498511628164974</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.113113559516075</v>
+        <v>0.08486168288378559</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.288888972653604</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.311289374871361</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.279941895176651</v>
+        <v>-7.350571586757375</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.05241065339094719</v>
+        <v>0.02415877675865774</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.268568056745046</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.203603001728327</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.255713258787678</v>
+        <v>-7.326342950368402</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.05338812169305829</v>
+        <v>0.02513624506076884</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.244339420356074</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.209426197308233</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.212164852016988</v>
+        <v>-7.282794543597712</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.06384687230624131</v>
+        <v>0.03559499567395186</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.244339420356074</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.202465585213139</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.97001645856313</v>
+        <v>-7.040646150143854</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1751685840689277</v>
+        <v>0.1469167074366382</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.244339420356074</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.216927939594282</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.906787086794782</v>
+        <v>-6.977416778375505</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1949924532354617</v>
+        <v>0.1667405766031722</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.244339420356074</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.211460060053478</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.783495951977651</v>
+        <v>-6.854125643558374</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2418070011728912</v>
+        <v>0.2135551245406018</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.121048285538944</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.282932834954333</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.762346753074207</v>
+        <v>-6.832976444654931</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2579676589715936</v>
+        <v>0.2297157823393041</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.0998990866355</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.303323332533724</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.518581311090763</v>
+        <v>-6.589211002671487</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3512545441120221</v>
+        <v>0.3230026674797326</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.0998990866355</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.299104040880775</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.371684283372893</v>
+        <v>-6.442313974953617</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4121376691191858</v>
+        <v>0.3838857924868964</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.052240844656912</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.329823299987944</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.121833889423819</v>
+        <v>-6.192463581004542</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5048199016825179</v>
+        <v>0.4765680250502284</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.052240844656912</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.322565374971646</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.945941796956387</v>
+        <v>-6.01657148853711</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5787758621901395</v>
+        <v>0.5505239855578501</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.052240844656912</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.326164498492294</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.774495333933923</v>
+        <v>-5.845125025514647</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6606819534536785</v>
+        <v>0.6324300768213891</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8807943816344491</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.442359882360326</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.5494623342651</v>
+        <v>-5.620092025845824</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7497156309375046</v>
+        <v>0.7214637543052151</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6557613819656263</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.576400159777917</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.485826592031166</v>
+        <v>-5.556456283611889</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7798647288853959</v>
+        <v>0.7516128522531065</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5921256397316917</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.619276406172595</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.392826550825268</v>
+        <v>-5.463456242405991</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7982590041515509</v>
+        <v>0.7700071275192615</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5921256397316917</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.60047066495639</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712286</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.152396054020407</v>
+        <v>-5.223025745601131</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8961742794983723</v>
+        <v>0.8679224028660828</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3516951429268315</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.746472039664184</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.080153485849213</v>
+        <v>-5.150783177429936</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9290006206016703</v>
+        <v>0.9007487439693809</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3516951429268315</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.750401353499004</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.964213636224027</v>
+        <v>-5.034843327804751</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9760551443690844</v>
+        <v>0.9478032677367949</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2748734119107076</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.797172976026018</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.8554087507443</v>
+        <v>-4.926038442325024</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.016575169780969</v>
+        <v>0.9883232931486794</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2748734119107076</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.794171047246012</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.63538795270729</v>
+        <v>-4.706017644288013</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.106162526006387</v>
+        <v>1.077910649374098</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1336535668427273</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.880481991297414</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.502520263644012</v>
+        <v>-4.573149955224736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.175203784433521</v>
+        <v>1.146951907801232</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1336535668427273</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.896376174099237</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.343005160124642</v>
+        <v>-4.413634851705366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.240155670281571</v>
+        <v>1.211903793649282</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.02586153667664259</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.993231080651161</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.198333015024905</v>
+        <v>-4.268962706605628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.308112630882906</v>
+        <v>1.279860754250617</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.17053368177638</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.090122470272444</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.258207842382597</v>
+        <v>-4.328837533963321</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.270200191341255</v>
+        <v>1.241948314708966</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1106588544186879</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.040235065259254</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.171408344603588</v>
+        <v>-4.242038036184312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.327320483775425</v>
+        <v>1.299068607143135</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1106588544186879</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06263555858182</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.173878051065394</v>
+        <v>-4.244507742646118</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.326405002564115</v>
+        <v>1.298153125931825</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1081891479568817</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.061226136078149</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.242248237389404</v>
+        <v>-4.312877928970128</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.310063850509212</v>
+        <v>1.281811973876923</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1174648469930967</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.07779847797458</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.120831807762928</v>
+        <v>-4.191461499343651</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.349067130991694</v>
+        <v>1.320815254359405</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1174648469930967</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.068235186606471</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.151824967091633</v>
+        <v>-4.222454658672357</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.161379432300599</v>
+        <v>1.13312755566831</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1174648469930967</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.892944751646858</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.976350707299164</v>
+        <v>-4.046980398879887</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.236136368209374</v>
+        <v>1.207884491577085</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1174648469930967</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.897511983638645</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.087286959940412</v>
+        <v>-4.157916651521136</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.167503895914082</v>
+        <v>1.139252019281793</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1174648469930967</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.873254012399852</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.290313537483645</v>
+        <v>-4.360943229064369</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.089424650116694</v>
+        <v>1.061172773484405</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.08556173055013672</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.754569451093818</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.132387938548352</v>
+        <v>-4.203017630129076</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.162767276122944</v>
+        <v>1.134515399490654</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.08556173055013672</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.76474183752595</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.046144475521975</v>
+        <v>-4.116774167102698</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.192210931907355</v>
+        <v>1.163959055275066</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.08556173055013672</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.759688108099811</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.047327560173036</v>
+        <v>-4.11795725175376</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.183513473491456</v>
+        <v>1.155261596859167</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.09120477901664825</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.748078054464429</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.924199853178953</v>
+        <v>-3.994829544759677</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.233316429322191</v>
+        <v>1.205064552689902</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.09120477901664825</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.748629927497531</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.831389371728094</v>
+        <v>-3.902019063308817</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.1997133137939</v>
+        <v>1.171461437161611</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.001605702434211098</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.733588908259412</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.782826319507063</v>
+        <v>-3.853456011087787</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.221012010606914</v>
+        <v>1.192760133974624</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.05016875465524129</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.764600215516631</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.670155101270813</v>
+        <v>-3.740784792851537</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.261156206413137</v>
+        <v>1.232904329780847</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1628399728914915</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.827278654970104</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268533</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.557778100088141</v>
+        <v>-3.628407791668864</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.311598302716873</v>
+        <v>1.283346426084583</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1628399728914915</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.832769950800771</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.756012668974871</v>
+        <v>-3.743638720883439</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.24380167693072</v>
+        <v>1.248751256167293</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.03539459599523909</v>
+        <v>-0.02302064790380404</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.725326411237272</v>
+        <v>2.732750780092133</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.83901395000015</v>
+        <v>-3.826640001908718</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.048956884521261</v>
+        <v>1.053906463757834</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.05396548052241285</v>
+        <v>-0.0415915324309778</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.552539600521621</v>
+        <v>2.559963969376482</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.679819677943574</v>
+        <v>-3.667445729852142</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.232784254063098</v>
+        <v>1.23773383329967</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.05396548052241285</v>
+        <v>-0.0415915324309778</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.672689261240827</v>
+        <v>2.680113630095688</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660764</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.766418260924677</v>
+        <v>-3.754044312833245</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.212657846972979</v>
+        <v>1.217607426209552</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.05396548052241285</v>
+        <v>-0.0415915324309778</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.68720228734315</v>
+        <v>2.694626656198011</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117049438342</v>
+        <v>3.741170494383418</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.728034598366526</v>
+        <v>-3.715660650275094</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.225430753338608</v>
+        <v>1.230380332575181</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01558181796426167</v>
+        <v>-0.003207869872826619</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.707651926220409</v>
+        <v>2.71507629507527</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002478</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.55091826833136</v>
+        <v>-3.538544320239927</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.293006314197977</v>
+        <v>1.29795589343455</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01558181796426167</v>
+        <v>-0.003207869872826619</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.704380955065711</v>
+        <v>2.711805323920572</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263898</v>
+        <v>3.741324873263895</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.521216144355066</v>
+        <v>-3.508842196263634</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.305570555550407</v>
+        <v>1.31052013478698</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.02005194317957504</v>
+        <v>-0.007677995088139988</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.702382271698436</v>
+        <v>2.709806640553297</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481232</v>
+        <v>3.750725801481227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.341840723116298</v>
+        <v>-3.329466775024866</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.371107699352329</v>
+        <v>1.376057278588902</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1367248149911436</v>
+        <v>0.1490987630825787</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.790235301907282</v>
+        <v>2.797659670762143</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452227</v>
+        <v>3.716988143452222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.386854936636904</v>
+        <v>-3.374480988545472</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.333909469275676</v>
+        <v>1.338859048512249</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.106375919676539</v>
+        <v>0.1187498677679741</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.752833420050109</v>
+        <v>2.76025778890497</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.65385944690934</v>
+        <v>-3.641485498817907</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.232799227505648</v>
+        <v>1.237748806742221</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08798711836640954</v>
+        <v>-0.07561317027497449</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.641907159563285</v>
+        <v>2.649331528418147</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230804</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.942646667368255</v>
+        <v>-3.930272719276823</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.116488261218583</v>
+        <v>1.121437840455156</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1890732384654099</v>
+        <v>-0.1766992903739749</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.580459409400387</v>
+        <v>2.587883778255248</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.910171081197483</v>
+        <v>-3.89779713310605</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.127078457241209</v>
+        <v>1.132028036477782</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1890732384654099</v>
+        <v>-0.1766992903739749</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.578059370954703</v>
+        <v>2.585483739809564</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.891132953490185</v>
+        <v>-3.878759005398753</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.131218427532373</v>
+        <v>1.136168006768945</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2472568497966044</v>
+        <v>-0.2348829017051694</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.539673923364231</v>
+        <v>2.547098292219093</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.922259584640803</v>
+        <v>-3.909885636549371</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.296349644010806</v>
+        <v>1.301299223247379</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2472568497966044</v>
+        <v>-0.2348829017051694</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.717255792302912</v>
+        <v>2.724680161157773</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.044171958305161</v>
+        <v>-4.030331171870587</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.248418023531196</v>
+        <v>1.253954338105026</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3204835234030043</v>
+        <v>-0.3164127394853966</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.674153117125206</v>
+        <v>2.676595587475771</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259116</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.18849486423008</v>
+        <v>-4.174654077795505</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.196697391558155</v>
+        <v>1.202233706131985</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3204835234030043</v>
+        <v>-0.3164127394853966</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.680161647522132</v>
+        <v>2.682604117872696</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.040751893995077</v>
+        <v>-4.026911107560503</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.334947227444178</v>
+        <v>1.340483542018007</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1526761661681211</v>
+        <v>-0.1486053822505134</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.859998709655084</v>
+        <v>2.862441180005648</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.802242353651162</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.142766576526299</v>
+        <v>-4.128925790091724</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.29693497596317</v>
+        <v>1.302471290537</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1526761661681211</v>
+        <v>-0.1486053822505134</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.862792331186565</v>
+        <v>2.865234801537129</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864727</v>
+        <v>3.805605409864722</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.006157232432207</v>
+        <v>-3.992316445997632</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.352241061992465</v>
+        <v>1.357777376566295</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.01606682207402865</v>
+        <v>-0.01199603815642092</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.945420286034679</v>
+        <v>2.947862756385243</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360611</v>
+        <v>3.798236219360608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.148922565254857</v>
+        <v>-4.135081778820282</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.294215405603516</v>
+        <v>1.299751720177345</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1588321548966791</v>
+        <v>-0.1547613709790713</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.858841563081199</v>
+        <v>2.861284033431763</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.867359061268419</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.086624566478735</v>
+        <v>-4.07278378004416</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.385470158910785</v>
+        <v>1.391006473484615</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1588321548966791</v>
+        <v>-0.1547613709790713</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.925177116878019</v>
+        <v>2.927619587228584</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.667501561709265</v>
+        <v>3.847249917546244</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.943287536270443</v>
+        <v>3.055393512868345</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.086624566478735</v>
+        <v>-4.07278378004416</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.385470158910785</v>
+        <v>1.391006473484615</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1588321548966791</v>
+        <v>-0.1547613709790713</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.936351333256811</v>
+        <v>3.048457309854713</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-9.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>447.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-568.9%</t>
+          <t>-596.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-97.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-237.1%</t>
+          <t>-248.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-716.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-137.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-239.5%</t>
+          <t>-262.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-141.2%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.72634584450566</v>
+        <v>-10.96327202262464</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.124623201359017</v>
+        <v>-1.219393672606606</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.741976701082425</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.521085540107541</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50050069178625</v>
+        <v>-10.73742686990522</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.024706067235044</v>
+        <v>-1.119476538482633</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.700050025495261</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.555820618496048</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.37592203544866</v>
+        <v>-10.61284821356763</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9737354601439487</v>
+        <v>-1.068505931391537</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.700050025495261</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.556959763052107</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42881732349295</v>
+        <v>-10.66574350161192</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9922598011995554</v>
+        <v>-1.087030272447143</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.695094679406815</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.562566744867283</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1449085925642</v>
+        <v>-10.38183477068317</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8729626045894197</v>
+        <v>-0.9677330758370077</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.695094679406815</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.568300449105919</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-10.31046837807352</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.9489237811870144</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.623728286797167</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.601383022277843</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-10.04663151086945</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.8532725156182939</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.623728286797167</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.591499540964935</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.779389710001055</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.7482103557703081</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.623728286797167</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.589664980465561</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781942</v>
+        <v>3.784680945781944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.681482671324565</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.7093478552731729</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.55574253693661</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.630156115408435</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.657529130348607</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.6990979327372959</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.531788995960653</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.645196746139503</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487766</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.39346919202581</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.6067342735699297</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.267729057637857</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.790372392971428</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.686389568520973</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.3266894578282953</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.267729057637857</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.787585359311127</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.646205270154782</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.3102721145939777</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-2.227544759271666</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.812039562218683</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.566135474616978</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.2788773751580993</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-2.147474963733862</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>1.859448260762122</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-8.332654252387378</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.1775604574284069</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.913993741504263</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.007461422937734</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-8.182987861379864</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>-0.1205861113383606</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.821090250261727</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.060311307370296</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-8.050712387748977</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>-0.07230843513897867</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.688814776630841</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.135044078295855</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.860112713075824</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.006746495417919274</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.498215101957688</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.252218943787384</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.611112914392243</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.1192527561150105</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.498215101957688</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.265125285011043</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.716702904165348</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>-0.05095916939345013</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.603805091730792</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.073795361547961</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.735437806283945</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>-0.00990878836380249</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.603805091730792</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.122339703425048</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.587497764876345</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>-0.07061169448893034</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.583484175822235</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.014653330282015</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.563269128487373</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>-0.06963422618681969</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.559255539433262</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.02047652586192</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.519720721716682</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>-0.05917547557363667</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.559255539433262</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.013515913766827</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-7.277572328262824</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.05214623618904968</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.559255539433262</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.02797826814797</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-7.214342956494476</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.07197010535558412</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.559255539433262</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.022510388607165</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-7.091051821677345</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.1187846532930132</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.435964404616132</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.09398316350802</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-7.069902622773902</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.134945311091716</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.414815205712689</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.114373661087411</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.826137180790457</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.2282321962321441</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.414815205712689</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.110154369434462</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.679240153072588</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.2891153212393083</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.367156963734101</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.14087362854163</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.429389759123513</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.3817975538026404</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.367156963734101</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.133615703525333</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-6.253497666656081</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.4557535143102616</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.367156963734101</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.137214827045981</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-6.082051203633617</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.537659605573801</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-1.195710500711638</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.253410210914013</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.857018203964794</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.6266932830576271</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.9706775010428147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.387450488331603</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.79338246173086</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.656842381005518</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.9070417588088802</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.430326734726282</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.700382420524962</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.675236656271673</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.9070417588088802</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.411520993510077</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712286</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.459951923720102</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.7731519316184947</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6666112620040199</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.557522368217871</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.387709355548907</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.8059782727217928</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6666112620040199</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.561451682052691</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349959</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-5.271769505923722</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.8530327964892068</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.589789530987896</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.608223304579705</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-5.162964620443995</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>0.8935528219010909</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.589789530987896</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.605221375799699</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.942943822406984</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>0.9831401781265094</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4485696859199158</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.691532319851101</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.810076133343706</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.052181436553644</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4485696859199158</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.707426502652925</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.650561029824337</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.117133322401693</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.2890545824005458</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.804281409204848</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.505888884724599</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.185090283003028</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>-0.1443824373008084</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>2.90117279882613</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.565763712082291</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.147177843461377</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.2042572646585005</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.851285393812941</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.478964214303282</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.204298135895547</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.2042572646585005</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>2.873685887135507</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.481433920765088</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.203382654684237</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>-0.2067269711203067</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>2.872276464631836</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.549804107089098</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.187041502629335</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1974512720840917</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>2.888848806528267</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.191461499343651</v>
+        <v>-4.428387677462622</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320815254359405</v>
+        <v>1.226044783111817</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1974512720840917</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>2.879285515160158</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.222454658672357</v>
+        <v>-4.459380836791327</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.13312755566831</v>
+        <v>1.038357084420721</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1974512720840917</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.703995080200545</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.046980398879887</v>
+        <v>-4.283906576998858</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207884491577085</v>
+        <v>1.113114020329497</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1974512720840917</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.708562312192333</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695437</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.157916651521136</v>
+        <v>-4.394842829640107</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.139252019281793</v>
+        <v>1.044481548034204</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1974512720840917</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.68430434095354</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.360943229064369</v>
+        <v>-4.59786940718334</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061172773484405</v>
+        <v>0.9664023022368167</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.4004778496273251</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.565619779647505</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.203017630129076</v>
+        <v>-4.439943808248047</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134515399490654</v>
+        <v>1.039744928243066</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.4004778496273251</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.575792166079637</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.116774167102698</v>
+        <v>-4.353700345221669</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163959055275066</v>
+        <v>1.069188584027478</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.4004778496273251</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.570738436653498</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.11795725175376</v>
+        <v>-4.35488342987273</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155261596859167</v>
+        <v>1.060491125611579</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.4061208980938367</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.559128383018116</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.994829544759677</v>
+        <v>-4.231755722878647</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205064552689902</v>
+        <v>1.110294081442313</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.4061208980938367</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.559680256051218</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.902019063308817</v>
+        <v>-4.138945241427788</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171461437161611</v>
+        <v>1.076690965914023</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.3133104166429773</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.544639236813099</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.853456011087787</v>
+        <v>-4.090382189206758</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192760133974624</v>
+        <v>1.097989662727036</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.2647473644219471</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.575650544070318</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.740784792851537</v>
+        <v>-3.977710970970508</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.232904329780847</v>
+        <v>1.138133858533259</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>-0.1520761461856969</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.638328983523791</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628407791668864</v>
+        <v>-3.865333969787835</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.283346426084583</v>
+        <v>1.188575954836995</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>-0.1520761461856969</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.643820279354459</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.743638720883439</v>
+        <v>-4.063568538674565</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.248751256167293</v>
+        <v>1.120779329050842</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.02302064790380404</v>
+        <v>-0.3503107150724275</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.732750780092133</v>
+        <v>2.536376739790959</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.826640001908718</v>
+        <v>-4.189670666414393</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.053906463757834</v>
+        <v>0.9086941979555641</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.0415915324309778</v>
+        <v>-0.4506058339892958</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.559963969376482</v>
+        <v>2.314555388441491</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199264</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.667445729852142</v>
+        <v>-4.030476394357818</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.23773383329967</v>
+        <v>1.0925215674974</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.0415915324309778</v>
+        <v>-0.4506058339892958</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.680113630095688</v>
+        <v>2.434705049160697</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.754044312833245</v>
+        <v>-4.117074977338921</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.217607426209552</v>
+        <v>1.072395160407282</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.0415915324309778</v>
+        <v>-0.4506058339892958</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.694626656198011</v>
+        <v>2.44921807526302</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383418</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.715660650275094</v>
+        <v>-4.07869131478077</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.230380332575181</v>
+        <v>1.085168066772911</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.003207869872826619</v>
+        <v>-0.4122221714311446</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.71507629507527</v>
+        <v>2.46966771414028</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.538544320239927</v>
+        <v>-3.901574984745603</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.29795589343455</v>
+        <v>1.152743627632279</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.003207869872826619</v>
+        <v>-0.4122221714311446</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.711805323920572</v>
+        <v>2.466396742985582</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.508842196263634</v>
+        <v>-3.87187286076931</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.31052013478698</v>
+        <v>1.16530786898471</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.007677995088139988</v>
+        <v>-0.416692296646458</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.709806640553297</v>
+        <v>2.464398059618306</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.329466775024866</v>
+        <v>-3.692497439530542</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.376057278588902</v>
+        <v>1.230845012786631</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1490987630825787</v>
+        <v>-0.2599155384757393</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.797659670762143</v>
+        <v>2.552251089827152</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.374480988545472</v>
+        <v>-3.737511653051148</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.338859048512249</v>
+        <v>1.193646782709979</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1187498677679741</v>
+        <v>-0.2902644337903439</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.76025778890497</v>
+        <v>2.514849207969979</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.641485498817907</v>
+        <v>-4.004516163323584</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.237748806742221</v>
+        <v>1.09253654093995</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.07561317027497449</v>
+        <v>-0.4846274718332925</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.649331528418147</v>
+        <v>2.403922947483156</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230804</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.930272719276823</v>
+        <v>-4.293303383782499</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.121437840455156</v>
+        <v>0.9762255746528854</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1766992903739749</v>
+        <v>-0.5857135919322929</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.587883778255248</v>
+        <v>2.342475197320257</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.89779713310605</v>
+        <v>-4.260827797611727</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.132028036477782</v>
+        <v>0.986815770675511</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1766992903739749</v>
+        <v>-0.5857135919322929</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.585483739809564</v>
+        <v>2.340075158874574</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.878759005398753</v>
+        <v>-4.24178966990443</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.136168006768945</v>
+        <v>0.9909557409666749</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2348829017051694</v>
+        <v>-0.6438972032634874</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.547098292219093</v>
+        <v>2.301689711284102</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.909885636549371</v>
+        <v>-4.272916301055048</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.301299223247379</v>
+        <v>1.156086957445108</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2348829017051694</v>
+        <v>-0.6438972032634874</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.724680161157773</v>
+        <v>2.479271580222782</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.030331171870587</v>
+        <v>-4.32523668165584</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.253954338105026</v>
+        <v>1.135992134190925</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3164127394853966</v>
+        <v>-0.6089503432546153</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.676595587475771</v>
+        <v>2.501073025214239</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259116</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.174654077795505</v>
+        <v>-4.469559587580759</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.202233706131985</v>
+        <v>1.084271502217883</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3164127394853966</v>
+        <v>-0.6089503432546153</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.682604117872696</v>
+        <v>2.507081555611165</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.026911107560503</v>
+        <v>-4.321816617345756</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.340483542018007</v>
+        <v>1.222521338103906</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1486053822505134</v>
+        <v>-0.4411429860197321</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.862441180005648</v>
+        <v>2.686918617744117</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651162</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.128925790091724</v>
+        <v>-4.423831299876977</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.302471290537</v>
+        <v>1.184509086622899</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1486053822505134</v>
+        <v>-0.4411429860197321</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.865234801537129</v>
+        <v>2.689712239275598</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864722</v>
+        <v>3.805605409864728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.992316445997632</v>
+        <v>-4.287221955782885</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.357777376566295</v>
+        <v>1.239815172652194</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.01199603815642092</v>
+        <v>-0.3045336419256396</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.947862756385243</v>
+        <v>2.772340194123712</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360608</v>
+        <v>3.798236219360614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.135081778820282</v>
+        <v>-4.429987288605535</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.299751720177345</v>
+        <v>1.181789516263244</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1547613709790713</v>
+        <v>-0.4472989747482901</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.861284033431763</v>
+        <v>2.685761471170232</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268419</v>
+        <v>3.867359061268425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.07278378004416</v>
+        <v>-4.367689289829412</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.391006473484615</v>
+        <v>1.273044269570514</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1547613709790713</v>
+        <v>-0.4472989747482901</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.927619587228584</v>
+        <v>2.752097024967052</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.847249917546244</v>
+        <v>3.72492876240328</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.055393512868345</v>
+        <v>3.023202282484761</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.07278378004416</v>
+        <v>-4.352192439345492</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.391006473484615</v>
+        <v>1.281968882432817</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1547613709790713</v>
+        <v>-0.3842097390460043</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.048457309854713</v>
+        <v>2.792676439057158</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240521.xlsx
+++ b/tame_output/ON/bt/strategyON_20240521.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-4.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.7%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.8%</t>
+          <t>-592.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-97.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-248.0%</t>
+          <t>-241.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.0%</t>
+          <t>-239.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-262.4%</t>
+          <t>-214.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-132.9%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.96327202262464</v>
+        <v>-10.72634584450566</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.219393672606606</v>
+        <v>-1.124623201359017</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.741976701082425</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.521085540107541</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.73742686990522</v>
+        <v>-10.76897940706263</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.119476538482633</v>
+        <v>-1.132097553345595</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.700050025495261</v>
+        <v>-2.471064685913785</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.555820618496048</v>
+        <v>1.693211822244934</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.61284821356763</v>
+        <v>-10.64440075072504</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.068505931391537</v>
+        <v>-1.0811269462545</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.700050025495261</v>
+        <v>-2.471064685913785</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.556959763052107</v>
+        <v>1.694350966800993</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.66574350161192</v>
+        <v>-10.69729603876933</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.087030272447143</v>
+        <v>-1.099651287310107</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.695094679406815</v>
+        <v>-2.466109339825339</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.562566744867283</v>
+        <v>1.699957948616168</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.38183477068317</v>
+        <v>-10.41338730784058</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9677330758370077</v>
+        <v>-0.9803540906999713</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.695094679406815</v>
+        <v>-2.466109339825339</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.568300449105919</v>
+        <v>1.705691652854805</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.31046837807352</v>
+        <v>-10.34202091523093</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9489237811870144</v>
+        <v>-0.961544796049977</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.623728286797167</v>
+        <v>-2.394742947215691</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.601383022277843</v>
+        <v>1.738774226026728</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.04663151086945</v>
+        <v>-10.07818404802686</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8532725156182939</v>
+        <v>-0.8658935304812565</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.623728286797167</v>
+        <v>-2.394742947215691</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.591499540964935</v>
+        <v>1.72889074471382</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.779389710001055</v>
+        <v>-9.810942247158463</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7482103557703081</v>
+        <v>-0.7608313706332717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.623728286797167</v>
+        <v>-2.394742947215691</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.589664980465561</v>
+        <v>1.727056184214447</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781944</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.681482671324565</v>
+        <v>-9.713035208481973</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7093478552731729</v>
+        <v>-0.721968870136136</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.55574253693661</v>
+        <v>-2.326757197355135</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.630156115408435</v>
+        <v>1.76754731915732</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.657529130348607</v>
+        <v>-9.689081667506015</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6990979327372959</v>
+        <v>-0.7117189476002594</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.531788995960653</v>
+        <v>-2.302803656379177</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.645196746139503</v>
+        <v>1.782587949888388</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.789307536487766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.39346919202581</v>
+        <v>-9.425021729183218</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6067342735699297</v>
+        <v>-0.6193552884328928</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.267729057637857</v>
+        <v>-2.038743718056381</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.790372392971428</v>
+        <v>1.927763596720314</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.686389568520973</v>
+        <v>-8.717942105678381</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3266894578282953</v>
+        <v>-0.3393104726912588</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.267729057637857</v>
+        <v>-2.038743718056381</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.787585359311127</v>
+        <v>1.924976563060013</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.646205270154782</v>
+        <v>-8.67775780731219</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3102721145939777</v>
+        <v>-0.3228931294569413</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.227544759271666</v>
+        <v>-1.99855941969019</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.812039562218683</v>
+        <v>1.949430765967568</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.566135474616978</v>
+        <v>-8.597688011774386</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2788773751580993</v>
+        <v>-0.2914983900210624</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.147474963733862</v>
+        <v>-1.918489624152386</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.859448260762122</v>
+        <v>1.996839464511008</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.332654252387378</v>
+        <v>-8.364206789544788</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1775604574284069</v>
+        <v>-0.1901814722913708</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.913993741504263</v>
+        <v>-1.685008401922788</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.007461422937734</v>
+        <v>2.144852626686619</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.182987861379864</v>
+        <v>-8.214540398537274</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1205861113383606</v>
+        <v>-0.1332071262013246</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.821090250261727</v>
+        <v>-1.592104910680252</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.060311307370296</v>
+        <v>2.197702511119182</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.050712387748977</v>
+        <v>-8.082264924906386</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.07230843513897867</v>
+        <v>-0.08492945000194263</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.688814776630841</v>
+        <v>-1.459829437049365</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.135044078295855</v>
+        <v>2.272435282044741</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.860112713075824</v>
+        <v>-7.891665250233234</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.006746495417919274</v>
+        <v>-0.00587451944504469</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.498215101957688</v>
+        <v>-1.269229762376212</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.252218943787384</v>
+        <v>2.389610147536269</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.611112914392243</v>
+        <v>-7.642665451549653</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1192527561150105</v>
+        <v>0.1066317412520466</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.498215101957688</v>
+        <v>-1.269229762376212</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.265125285011043</v>
+        <v>2.402516488759928</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.716702904165348</v>
+        <v>-7.748255441322757</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05095916939345013</v>
+        <v>-0.0635801842564141</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.603805091730792</v>
+        <v>-1.374819752149317</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.073795361547961</v>
+        <v>2.211186565296847</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.735437806283945</v>
+        <v>-7.766990343441354</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.00990878836380249</v>
+        <v>-0.02252980322676645</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.603805091730792</v>
+        <v>-1.374819752149317</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.122339703425048</v>
+        <v>2.259730907173933</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.587497764876345</v>
+        <v>-7.619050302033755</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07061169448893034</v>
+        <v>-0.08323270935189431</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.583484175822235</v>
+        <v>-1.354498836240759</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.014653330282015</v>
+        <v>2.1520445340309</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.563269128487373</v>
+        <v>-7.594821665644782</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06963422618681969</v>
+        <v>-0.08225524104978366</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.559255539433262</v>
+        <v>-1.330270199851787</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.02047652586192</v>
+        <v>2.157867729610805</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.519720721716682</v>
+        <v>-7.551273258874092</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05917547557363667</v>
+        <v>-0.07179649043660064</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.559255539433262</v>
+        <v>-1.330270199851787</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.013515913766827</v>
+        <v>2.150907117515712</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.277572328262824</v>
+        <v>-7.309124865420234</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05214623618904968</v>
+        <v>0.03952522132608571</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.559255539433262</v>
+        <v>-1.330270199851787</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.02797826814797</v>
+        <v>2.165369471896855</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.214342956494476</v>
+        <v>-7.245895493651886</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07197010535558412</v>
+        <v>0.05934909049262016</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.559255539433262</v>
+        <v>-1.330270199851787</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.022510388607165</v>
+        <v>2.15990159235605</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.091051821677345</v>
+        <v>-7.122604358834755</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1187846532930132</v>
+        <v>0.1061636384300493</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.435964404616132</v>
+        <v>-1.206979065034656</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.09398316350802</v>
+        <v>2.231374367256905</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389912</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.069902622773902</v>
+        <v>-7.101455159931311</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.134945311091716</v>
+        <v>0.1223242962287521</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.414815205712689</v>
+        <v>-1.185829866131213</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.114373661087411</v>
+        <v>2.251764864836296</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.826137180790457</v>
+        <v>-6.857689717947867</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2282321962321441</v>
+        <v>0.2156111813691806</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.414815205712689</v>
+        <v>-1.185829866131213</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.110154369434462</v>
+        <v>2.247545573183347</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.679240153072588</v>
+        <v>-6.710792690229997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2891153212393083</v>
+        <v>0.2764943063763443</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.367156963734101</v>
+        <v>-1.138171624152625</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14087362854163</v>
+        <v>2.278264832290516</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.429389759123513</v>
+        <v>-6.460942296280923</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3817975538026404</v>
+        <v>0.3691765389396764</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.367156963734101</v>
+        <v>-1.138171624152625</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.133615703525333</v>
+        <v>2.271006907274218</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.253497666656081</v>
+        <v>-6.285050203813491</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4557535143102616</v>
+        <v>0.443132499447298</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.367156963734101</v>
+        <v>-1.138171624152625</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.137214827045981</v>
+        <v>2.274606030794867</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.082051203633617</v>
+        <v>-6.113603740791027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.537659605573801</v>
+        <v>0.525038590710837</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.195710500711638</v>
+        <v>-0.9667251611301618</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.253410210914013</v>
+        <v>2.390801414662898</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.857018203964794</v>
+        <v>-5.888570741122204</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6266932830576271</v>
+        <v>0.6140722681946631</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9706775010428147</v>
+        <v>-0.741692161461339</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.387450488331603</v>
+        <v>2.524841692080489</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353073</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.79338246173086</v>
+        <v>-5.82493499888827</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.656842381005518</v>
+        <v>0.6442213661425544</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9070417588088802</v>
+        <v>-0.6780564192274044</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.430326734726282</v>
+        <v>2.567717938475167</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544782</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.700382420524962</v>
+        <v>-5.731934957682371</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.675236656271673</v>
+        <v>0.662615641408709</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9070417588088802</v>
+        <v>-0.6780564192274044</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.411520993510077</v>
+        <v>2.548912197258963</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712286</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.459951923720102</v>
+        <v>-5.491504460877511</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7731519316184947</v>
+        <v>0.7605309167555308</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6666112620040199</v>
+        <v>-0.4376259224225442</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.557522368217871</v>
+        <v>2.694913571966756</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.387709355548907</v>
+        <v>-5.419261892706317</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8059782727217928</v>
+        <v>0.7933572578588288</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6666112620040199</v>
+        <v>-0.4376259224225442</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.561451682052691</v>
+        <v>2.698842885801576</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.271769505923722</v>
+        <v>-5.303322043081131</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8530327964892068</v>
+        <v>0.8404117816262429</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.589789530987896</v>
+        <v>-0.3608041914064203</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.608223304579705</v>
+        <v>2.745614508328591</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.162964620443995</v>
+        <v>-5.194517157601404</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8935528219010909</v>
+        <v>0.8809318070381273</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.589789530987896</v>
+        <v>-0.3608041914064203</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.605221375799699</v>
+        <v>2.742612579548584</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.942943822406984</v>
+        <v>-4.974496359564394</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9831401781265094</v>
+        <v>0.9705191632635455</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4485696859199158</v>
+        <v>-0.21958434633844</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.691532319851101</v>
+        <v>2.828923523599987</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.810076133343706</v>
+        <v>-4.841628670501116</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.052181436553644</v>
+        <v>1.03956042169068</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4485696859199158</v>
+        <v>-0.21958434633844</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.707426502652925</v>
+        <v>2.84481770640181</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966261</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.650561029824337</v>
+        <v>-4.682113566981746</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.117133322401693</v>
+        <v>1.10451230753873</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2890545824005458</v>
+        <v>-0.06006924281907011</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.804281409204848</v>
+        <v>2.941672612953734</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.505888884724599</v>
+        <v>-4.537441421882009</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.185090283003028</v>
+        <v>1.172469268140065</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1443824373008084</v>
+        <v>0.0846029022806673</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.90117279882613</v>
+        <v>3.038564002575016</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412107</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.565763712082291</v>
+        <v>-4.597316249239701</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.147177843461377</v>
+        <v>1.134556828598413</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2042572646585005</v>
+        <v>0.02472807492297519</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.851285393812941</v>
+        <v>2.988676597561827</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.478964214303282</v>
+        <v>-4.510516751460692</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.204298135895547</v>
+        <v>1.191677121032583</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2042572646585005</v>
+        <v>0.02472807492297519</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.873685887135507</v>
+        <v>3.011077090884393</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.481433920765088</v>
+        <v>-4.512986457922498</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.203382654684237</v>
+        <v>1.190761639821273</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2067269711203067</v>
+        <v>0.02225836846116902</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.872276464631836</v>
+        <v>3.009667668380721</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.549804107089098</v>
+        <v>-4.581356644246508</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.187041502629335</v>
+        <v>1.174420487766371</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1974512720840917</v>
+        <v>0.03153406749738397</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.888848806528267</v>
+        <v>3.026240010277152</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417556397837</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.428387677462622</v>
+        <v>-4.459940214620032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.226044783111817</v>
+        <v>1.213423768248853</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1974512720840917</v>
+        <v>0.03153406749738397</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.879285515160158</v>
+        <v>3.016676718909043</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.459380836791327</v>
+        <v>-4.490933373948737</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.038357084420721</v>
+        <v>1.025736069557758</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1974512720840917</v>
+        <v>0.03153406749738397</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.703995080200545</v>
+        <v>2.84138628394943</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.283906576998858</v>
+        <v>-4.315459114156267</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.113114020329497</v>
+        <v>1.100493005466533</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1974512720840917</v>
+        <v>0.03153406749738397</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.708562312192333</v>
+        <v>2.845953515941218</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.394842829640107</v>
+        <v>-4.426395366797516</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.044481548034204</v>
+        <v>1.03186053317124</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1974512720840917</v>
+        <v>0.03153406749738397</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.68430434095354</v>
+        <v>2.821695544702425</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.59786940718334</v>
+        <v>-4.629421944340749</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9664023022368167</v>
+        <v>0.9537812873738529</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4004778496273251</v>
+        <v>-0.1714925100458494</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.565619779647505</v>
+        <v>2.70301098339639</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734162</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.439943808248047</v>
+        <v>-4.471496345405456</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.039744928243066</v>
+        <v>1.027123913380102</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4004778496273251</v>
+        <v>-0.1714925100458494</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.575792166079637</v>
+        <v>2.713183369828523</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212299</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.353700345221669</v>
+        <v>-4.385252882379079</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.069188584027478</v>
+        <v>1.056567569164514</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4004778496273251</v>
+        <v>-0.1714925100458494</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.570738436653498</v>
+        <v>2.708129640402383</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.35488342987273</v>
+        <v>-4.38643596703014</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.060491125611579</v>
+        <v>1.047870110748615</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4061208980938367</v>
+        <v>-0.177135558512361</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.559128383018116</v>
+        <v>2.696519586767002</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.231755722878647</v>
+        <v>-4.263308260036057</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.110294081442313</v>
+        <v>1.097673066579349</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4061208980938367</v>
+        <v>-0.177135558512361</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.559680256051218</v>
+        <v>2.697071459800104</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.138945241427788</v>
+        <v>-4.170497778585197</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.076690965914023</v>
+        <v>1.064069951051059</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3133104166429773</v>
+        <v>-0.08432507706150161</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.544639236813099</v>
+        <v>2.682030440561984</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.090382189206758</v>
+        <v>-4.121934726364167</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.097989662727036</v>
+        <v>1.085368647864072</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2647473644219471</v>
+        <v>-0.03576202484047142</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.575650544070318</v>
+        <v>2.713041747819203</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.977710970970508</v>
+        <v>-4.009263508127917</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.138133858533259</v>
+        <v>1.125512843670295</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1520761461856969</v>
+        <v>0.07690919339577879</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.638328983523791</v>
+        <v>2.775720187272677</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.865333969787835</v>
+        <v>-3.896886506945245</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.188575954836995</v>
+        <v>1.175954939974031</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1520761461856969</v>
+        <v>0.07690919339577879</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.643820279354459</v>
+        <v>2.781211483103344</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.063568538674565</v>
+        <v>-4.095121075831975</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.120779329050842</v>
+        <v>1.108158314187878</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3503107150724275</v>
+        <v>-0.1213253754909518</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.536376739790959</v>
+        <v>2.673767943539845</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.189670666414393</v>
+        <v>-4.178122356857254</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9086941979555641</v>
+        <v>0.9133135217784198</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4506058339892958</v>
+        <v>-0.1398962600181256</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.314555388441491</v>
+        <v>2.500981132824194</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.030476394357818</v>
+        <v>-4.290916924865703</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.0925215674974</v>
+        <v>0.9883453552942458</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4506058339892958</v>
+        <v>-0.1398962600181256</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.434705049160697</v>
+        <v>2.621130793543399</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.117074977338921</v>
+        <v>-4.377515507846806</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.072395160407282</v>
+        <v>0.9682189482041275</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4506058339892958</v>
+        <v>-0.1398962600181256</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.44921807526302</v>
+        <v>2.635643819645722</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.07869131478077</v>
+        <v>-4.339131845288655</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.085168066772911</v>
+        <v>0.9809918545697567</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4122221714311446</v>
+        <v>-0.1015125974599744</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.46966771414028</v>
+        <v>2.656093458522982</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.75114362200248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.901574984745603</v>
+        <v>-4.162015515253489</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.152743627632279</v>
+        <v>1.048567415429125</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4122221714311446</v>
+        <v>-0.1015125974599744</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.466396742985582</v>
+        <v>2.652822487368284</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.87187286076931</v>
+        <v>-4.132313391277195</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.16530786898471</v>
+        <v>1.061131656781556</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.416692296646458</v>
+        <v>-0.1059827226752877</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.464398059618306</v>
+        <v>2.650823804001009</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.692497439530542</v>
+        <v>-3.952937970038428</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.230845012786631</v>
+        <v>1.126668800583477</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2599155384757393</v>
+        <v>0.05079403549543093</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.552251089827152</v>
+        <v>2.738676834209854</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.716988143452225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.737511653051148</v>
+        <v>-3.997952183559034</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.193646782709979</v>
+        <v>1.089470570506824</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2902644337903439</v>
+        <v>0.02044514018082633</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.514849207969979</v>
+        <v>2.701274952352681</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.004516163323584</v>
+        <v>-4.264956693831469</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.09253654093995</v>
+        <v>0.9883603287367959</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4846274718332925</v>
+        <v>-0.1739178978621223</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.403922947483156</v>
+        <v>2.590348691865858</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.293303383782499</v>
+        <v>-4.553743914290385</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9762255746528854</v>
+        <v>0.8720493624497312</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5857135919322929</v>
+        <v>-0.2750040179611226</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.342475197320257</v>
+        <v>2.528900941702959</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.260827797611727</v>
+        <v>-4.521268328119612</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.986815770675511</v>
+        <v>0.8826395584723568</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5857135919322929</v>
+        <v>-0.2750040179611226</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.340075158874574</v>
+        <v>2.526500903257276</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.24178966990443</v>
+        <v>-4.502230200412315</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9909557409666749</v>
+        <v>0.8867795287635207</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6438972032634874</v>
+        <v>-0.3331876292923172</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.301689711284102</v>
+        <v>2.488115455666804</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.272916301055048</v>
+        <v>-4.533356831562934</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.156086957445108</v>
+        <v>1.051910745241954</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6438972032634874</v>
+        <v>-0.3331876292923172</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.479271580222782</v>
+        <v>2.665697324605484</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.32523668165584</v>
+        <v>-4.585677212163725</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.135992134190925</v>
+        <v>1.031815921987771</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6089503432546153</v>
+        <v>-0.298240769283445</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.501073025214239</v>
+        <v>2.687498769596941</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.469559587580759</v>
+        <v>-4.644713025895185</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.084271502217883</v>
+        <v>1.014210126892113</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6089503432546153</v>
+        <v>-0.298240769283445</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.507081555611165</v>
+        <v>2.693507299993867</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.321816617345756</v>
+        <v>-4.496970055660182</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.222521338103906</v>
+        <v>1.152459962778136</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4411429860197321</v>
+        <v>-0.1304334120485618</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.686918617744117</v>
+        <v>2.873344362126819</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.802242353651166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.423831299876977</v>
+        <v>-4.598984738191404</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.184509086622899</v>
+        <v>1.114447711297128</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4411429860197321</v>
+        <v>-0.1304334120485618</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.689712239275598</v>
+        <v>2.8761379836583</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864728</v>
+        <v>3.805605409864725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.287221955782885</v>
+        <v>-4.462375394097311</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239815172652194</v>
+        <v>1.169753797326424</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3045336419256396</v>
+        <v>0.00617593204553063</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.772340194123712</v>
+        <v>2.958765938506414</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360614</v>
+        <v>3.798236219360612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.429987288605535</v>
+        <v>-4.605140726919961</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.181789516263244</v>
+        <v>1.111728140937474</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4472989747482901</v>
+        <v>-0.1365894007771198</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.685761471170232</v>
+        <v>2.872187215552934</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268425</v>
+        <v>3.867359061268423</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.367689289829412</v>
+        <v>-4.542842728143839</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.273044269570514</v>
+        <v>1.202982894244744</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4472989747482901</v>
+        <v>-0.1365894007771198</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.752097024967052</v>
+        <v>2.938522769349755</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.72492876240328</v>
+        <v>3.427949033855534</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.023202282484761</v>
+        <v>3.073848505488833</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.352192439345492</v>
+        <v>-4.310364149767652</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.281968882432817</v>
+        <v>1.349346421268025</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3842097390460043</v>
+        <v>0.09588917759906712</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.792676439057158</v>
+        <v>3.131382012048274</v>
       </c>
     </row>
   </sheetData>
